--- a/bases de datos planes y programas/planes_artes_visuales.xlsx
+++ b/bases de datos planes y programas/planes_artes_visuales.xlsx
@@ -9,7 +9,9 @@
   <sheets>
     <sheet name="Planes Curriculares" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Planes Curriculares'!$A$1:$G$101</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -469,12 +471,12 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="50" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="60" customWidth="1" min="7" max="7"/>
+    <col width="52" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="64" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -527,25 +529,65 @@
       </c>
       <c r="C2" s="3" t="inlineStr">
         <is>
+          <t>EXPRESAR Y CREAR VISUALMENTE</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>OA 1</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Expresar y crear trabajos de arte a partir de la observación del: › entorno natural: paisaje, animales y plantas › entorno cultural: vida cotidiana y familiar › entorno artístico: obras de arte local, chileno, latinoamericano y del resto del mundo</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>• Desarrollan ideas para sus trabajos de arte mediante la observación de imágenes, obras de arte, cuentos e imaginación.
+• Describen imágenes y obras con temas cotidianos del arte chileno, latinoamericano y del resto del mundo.
+• Expresan sus gustos personales por medio de pinturas y esculturas sobre su vida cotidiana (por ejemplo: comidas y juguetes preferidos, mascotas, entre otros).
+• Crean trabajos de arte basados en: - temas cotidianos y experiencias vividas (por ejemplo: paseo al campo, la playa, visita a un familiar, entre otros) - narraciones de cuentos tradicionales y modernos - temas de la vida cotidiana chilena (por ejemplo: fiestas, costumbres, juegos, deportes, entre otros) - su propia imaginación</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>1° Básico</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
           <t>Expresar y crear visualmente</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>OA 1</t>
         </is>
       </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Expresar y crear trabajos de arte a partir de la observación del: › entorno natural: paisaje, animales y plantas › entorno cultural: vida cotidiana y familiar › entorno artístico: obras de arte local, chileno, latinoamericano y del resto del mundo</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>• Desarrollan ideas para sus trabajos de arte, basándose en sus experiencias e imaginación.
 • Identifican características personales y las expresan en trabajos de arte (aspecto físico, rasgos de carácter).
@@ -567,38 +609,85 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>1° Básico</t>
         </is>
       </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>EXPRESAR Y CREAR VISUALMENTE</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>OA 2</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Experimentar y aplicar elementos del lenguaje visual en sus trabajos de arte: › línea (gruesa, delgada, recta, ondulada e irregular) › color (puro, mezclado, fríos y cálidos) › textura (visual y táctil)</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Aplicar</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>• Identifican y dan ejemplos de diversos tipos de líneas (gruesa, delgada, recta, ondulada, irregular, otras) en ilustraciones y/o su entorno.
+• Asocian emociones y sensaciones con diferentes tipos de líneas.
+• Experimentan con diferentes tipos de líneas en sus trabajos de arte.
+• Aplican diferentes tipos de líneas en sus dibujos y pinturas para expresar diferentes sensaciones y emociones (por ejemplo: lluvia, relámpago, viento, nube, entre otros.).
+• Identifican y dan ejemplos de colores puros y mezclados a partir de la observación del entorno y de obras de arte.
+• Experimentan mezclando colores puros y/o mezclados.
+• Realizan trabajos de pintura, aplicando colores puros y mezclados de forma intencionada para expresar: - sensaciones (oscuridad, claridad, fuertes, apagados, entre otros) - emociones (por ejemplo: alegría, pena, tranquilidad, rabia, entre otros)
+• Identifican y dan ejemplos de texturas táctiles y visuales en el entorno y en obras de arte.
+• Describen, en imágenes del entorno natural, texturas visuales y táctiles, considerando formas y colores (por ejemplo: hojas, pieles de animales, piedras, entre otros).
+• Experimentan con texturas táctiles, usando diferentes materiales (por ejemplo: piedras, algodón, diversos tipos de géneros, entre otros).
+• Aplican texturas táctiles y visuales en collages y dibujos digitales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>1° Básico</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Expresar y crear visualmente</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>OA 2</t>
         </is>
       </c>
-      <c r="E3" s="5" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Experimentar y aplicar elementos del lenguaje visual en sus trabajos de arte: › línea (gruesa, delgada, recta, ondulada e irregular) › color (puro, mezclado, fríos y cálidos) › textura (visual y táctil)</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>Aplicar</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>• Identifican y dan ejemplos de diversos tipos de líneas (gruesa, delgada, recta, ondulada, irregular, otras) en ilustraciones y/o su entorno.
 • Asocian emociones y sensaciones con diferentes tipos de líneas.
@@ -617,38 +706,84 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>1° Básico</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>EXPRESAR Y CREAR VISUALMENTE</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>OA 3</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Expresar emociones e ideas en sus trabajos de arte a partir de la experimentación con: › materiales de modelado, de reciclaje, naturales, papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales › herramientas para dibujar, pintar, cortar, modelar, unir y tecnológicas (pincel, tijera, esteca, computador, entre otras) › procedimientos de dibujo, pintura, collage, escultura, dibujo digital y otros</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Aplicar</t>
+        </is>
+      </c>
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>• Distinguen diferentes emociones y las expresan en trabajos de arte.
+• Usan diferentes materiales y herramientas para pintar y realizar esculturas (lápices de cera, pastel graso, plumones, témperas, acuarela, témpera con cola fría, greda, plasticina, papel maché, entre otros).
+• Experimentan con procedimientos de pintura y escultura.
+• Expresan emociones e ideas en pinturas y esculturas de: - animales y paisajes chilenos - experiencias y temas familiares
+• Distinguen diferentes emociones y las expresan en ideas para sus trabajos de arte mediante la observación de imágenes, obras de arte, poesías o su imaginación.
+• Experimentan con procedimientos de dibujo digital y collage, usando diversos materiales y herramientas.
+• Usan diferentes materiales y herramientas para realizar collage (papeles de diferentes tipos, plasticina, material de reciclaje, entre otros).
+• Expresan emociones e ideas en collages y dibujos digitales acerca de historias, experiencias y temas personales.
+• Crean collages y dibujos digitales acerca de animales y paisajes chilenos.
+• Expresan emociones e ideas mediante collages y dibujos digitales, utilizando diversos materiales y herramientas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>1° Básico</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Expresar y crear visualmente</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>OA 3</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Expresar emociones e ideas en sus trabajos de arte a partir de la experimentación con: › materiales de modelado, de reciclaje, naturales, papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales › herramientas para dibujar, pintar, cortar, modelar, unir y tecnológicas (pincel, tijera, esteca, computador, entre otras) › procedimientos de dibujo, pintura, collage, escultura, dibujo digital y otros</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>• Nombran diferentes emociones y las expresan en sus trabajos de arte.
 • Usan diferentes materiales y herramientas para dibujar y pintar (lápiz grafito, lápices de cera, pastel graso, plumones, témperas, acuarela, témpera con cola fría, entre otros).
@@ -667,38 +802,78 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>1° Básico</t>
         </is>
       </c>
-      <c r="B5" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>APRECIAR Y RESPONDER FRENTE AL ARTE</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>OA 4</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Observar y comunicar oralmente sus primeras impresiones de lo que sienten y piensan de obras de arte por variados medios. (Observar anualmente al menos 10 obras de arte local o chileno, 10 latinoamericanas y 10 de arte universal).</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Comprender</t>
+        </is>
+      </c>
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>• Identifican situaciones, paisajes y objetos en obras de arte.
+• Comunican lo que sienten y piensan de los trabajos de arte (por ejemplo: alegría, susto, tranquilidad, entre otros).
+• Comunican sus primeras impresiones acerca de obras de arte, usando diferentes medios (por ejemplo: sonidos, expresión corporal, entre otros).
+• Describen colores, formas, situaciones, paisajes y objetos en obras de arte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>1° Básico</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Apreciar y responder frente al arte</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>OA 4</t>
         </is>
       </c>
-      <c r="E5" s="5" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Observar y comunicar oralmente sus primeras impresiones de lo que sienten y piensan de obras de arte por variados medios. (Observar anualmente al menos 10 obras de arte local o chileno, 10 latinoamericanas y 10 de arte universal).</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>Comprender</t>
         </is>
       </c>
-      <c r="G5" s="5" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
         <is>
           <t>• Identifican situaciones, paisajes y objetos en obras de arte.
 • Comunican lo que sienten y piensan de los trabajos de arte (por ejemplo: alegría, susto, tranquilidad, entre otros).
@@ -709,38 +884,86 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>1° Básico</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C6" s="3" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>APRECIAR Y RESPONDER FRENTE AL ARTE</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>OA 5</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Explicar sus preferencias frente al trabajo de arte personal y de sus pares, usando elementos del lenguaje visual.</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Analizar</t>
+        </is>
+      </c>
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>• Exponen trabajos de arte, comunicando sus preferencias.
+• Hablan de los trabajos que más les gustan.
+• Describen trabajos de arte en relación con: - las emociones y sensaciones que transmiten - la aplicación de tipos de líneas con diferentes propósitos expresivos
+• Respetan los comentarios que hacen sus compañeros de trabajos de arte.
+• Describen trabajos de arte, considerando: - situaciones, paisajes y objetos en trabajos de arte - el uso de colores puros y mezclados con diferentes propósitos expresivos
+• Describen elementos originales en sus trabajos.
+• Explican preferencias frente a trabajos de arte con relación al uso del color.
+• Seleccionan, ayudados por el profesor, trabajos de arte para ser expuestos en el establecimiento o en la página web.
+• Reconocen y describen el uso de líneas, colores (fríos y cálidos) y texturas (visuales y táctiles) en su trabajo de arte personal y en el de sus pares.
+• Describen las emociones e historias expresadas por sus compañeros en trabajos de arte.
+• Respetan los trabajos de arte personales y de otros y la selección que hacen sus compañeros de estos.
+• Explican preferencias frente a trabajos de arte personal y de sus pares.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>1° Básico</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>Apreciar y responder frente al arte</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>OA 5</t>
         </is>
       </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Explicar sus preferencias frente al trabajo de arte personal y de sus pares, usando elementos del lenguaje visual.</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
         <is>
           <t>Analizar</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G11" s="5" t="inlineStr">
         <is>
           <t>• Exponen trabajos de arte, comunicando sus preferencias.
 • Hablan de los trabajos que más les gustan.
@@ -760,227 +983,6 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>1° Básico</t>
-        </is>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C7" s="5" t="inlineStr">
-        <is>
-          <t>EXPRESAR Y CREAR VISUALMENTE</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="inlineStr">
-        <is>
-          <t>OA 1</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr">
-        <is>
-          <t>Expresar y crear trabajos de arte a partir de la observación del: › entorno natural: paisaje, animales y plantas › entorno cultural: vida cotidiana y familiar › entorno artístico: obras de arte local, chileno, latinoamericano y del resto del mundo</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G7" s="5" t="inlineStr">
-        <is>
-          <t>• Desarrollan ideas para sus trabajos de arte mediante la observación de imágenes, obras de arte, cuentos e imaginación.
-• Describen imágenes y obras con temas cotidianos del arte chileno, latinoamericano y del resto del mundo.
-• Expresan sus gustos personales por medio de pinturas y esculturas sobre su vida cotidiana (por ejemplo: comidas y juguetes preferidos, mascotas, entre otros).
-• Crean trabajos de arte basados en: - temas cotidianos y experiencias vividas (por ejemplo: paseo al campo, la playa, visita a un familiar, entre otros) - narraciones de cuentos tradicionales y modernos - temas de la vida cotidiana chilena (por ejemplo: fiestas, costumbres, juegos, deportes, entre otros) - su propia imaginación</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>1° Básico</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C8" s="3" t="inlineStr">
-        <is>
-          <t>EXPRESAR Y CREAR VISUALMENTE</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>OA 2</t>
-        </is>
-      </c>
-      <c r="E8" s="3" t="inlineStr">
-        <is>
-          <t>Experimentar y aplicar elementos del lenguaje visual en sus trabajos de arte: › línea (gruesa, delgada, recta, ondulada e irregular) › color (puro, mezclado, fríos y cálidos) › textura (visual y táctil)</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Aplicar</t>
-        </is>
-      </c>
-      <c r="G8" s="3" t="inlineStr">
-        <is>
-          <t>• Identifican y dan ejemplos de diversos tipos de líneas (gruesa, delgada, recta, ondulada, irregular, otras) en ilustraciones y/o su entorno.
-• Asocian emociones y sensaciones con diferentes tipos de líneas.
-• Experimentan con diferentes tipos de líneas en sus trabajos de arte.
-• Aplican diferentes tipos de líneas en sus dibujos y pinturas para expresar diferentes sensaciones y emociones (por ejemplo: lluvia, relámpago, viento, nube, entre otros.).
-• Identifican y dan ejemplos de colores puros y mezclados a partir de la observación del entorno y de obras de arte.
-• Experimentan mezclando colores puros y/o mezclados.
-• Realizan trabajos de pintura, aplicando colores puros y mezclados de forma intencionada para expresar: - sensaciones (oscuridad, claridad, fuertes, apagados, entre otros) - emociones (por ejemplo: alegría, pena, tranquilidad, rabia, entre otros)
-• Identifican y dan ejemplos de texturas táctiles y visuales en el entorno y en obras de arte.
-• Describen, en imágenes del entorno natural, texturas visuales y táctiles, considerando formas y colores (por ejemplo: hojas, pieles de animales, piedras, entre otros).
-• Experimentan con texturas táctiles, usando diferentes materiales (por ejemplo: piedras, algodón, diversos tipos de géneros, entre otros).
-• Aplican texturas táctiles y visuales en collages y dibujos digitales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>1° Básico</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>EXPRESAR Y CREAR VISUALMENTE</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>OA 3</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr">
-        <is>
-          <t>Expresar emociones e ideas en sus trabajos de arte a partir de la experimentación con: › materiales de modelado, de reciclaje, naturales, papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales › herramientas para dibujar, pintar, cortar, modelar, unir y tecnológicas (pincel, tijera, esteca, computador, entre otras) › procedimientos de dibujo, pintura, collage, escultura, dibujo digital y otros</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
-          <t>Aplicar</t>
-        </is>
-      </c>
-      <c r="G9" s="5" t="inlineStr">
-        <is>
-          <t>• Distinguen diferentes emociones y las expresan en trabajos de arte.
-• Usan diferentes materiales y herramientas para pintar y realizar esculturas (lápices de cera, pastel graso, plumones, témperas, acuarela, témpera con cola fría, greda, plasticina, papel maché, entre otros).
-• Experimentan con procedimientos de pintura y escultura.
-• Expresan emociones e ideas en pinturas y esculturas de: - animales y paisajes chilenos - experiencias y temas familiares
-• Distinguen diferentes emociones y las expresan en ideas para sus trabajos de arte mediante la observación de imágenes, obras de arte, poesías o su imaginación.
-• Experimentan con procedimientos de dibujo digital y collage, usando diversos materiales y herramientas.
-• Usan diferentes materiales y herramientas para realizar collage (papeles de diferentes tipos, plasticina, material de reciclaje, entre otros).
-• Expresan emociones e ideas en collages y dibujos digitales acerca de historias, experiencias y temas personales.
-• Crean collages y dibujos digitales acerca de animales y paisajes chilenos.
-• Expresan emociones e ideas mediante collages y dibujos digitales, utilizando diversos materiales y herramientas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>1° Básico</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C10" s="3" t="inlineStr">
-        <is>
-          <t>APRECIAR Y RESPONDER FRENTE AL ARTE</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>OA 4</t>
-        </is>
-      </c>
-      <c r="E10" s="3" t="inlineStr">
-        <is>
-          <t>Observar y comunicar oralmente sus primeras impresiones de lo que sienten y piensan de obras de arte por variados medios. (Observar anualmente al menos 10 obras de arte local o chileno, 10 latinoamericanas y 10 de arte universal).</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Comprender</t>
-        </is>
-      </c>
-      <c r="G10" s="3" t="inlineStr">
-        <is>
-          <t>• Identifican situaciones, paisajes y objetos en obras de arte.
-• Comunican lo que sienten y piensan de los trabajos de arte (por ejemplo: alegría, susto, tranquilidad, entre otros).
-• Comunican sus primeras impresiones acerca de obras de arte, usando diferentes medios (por ejemplo: sonidos, expresión corporal, entre otros).
-• Describen colores, formas, situaciones, paisajes y objetos en obras de arte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>1° Básico</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C11" s="5" t="inlineStr">
-        <is>
-          <t>APRECIAR Y RESPONDER FRENTE AL ARTE</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>OA 5</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr">
-        <is>
-          <t>Explicar sus preferencias frente al trabajo de arte personal y de sus pares, usando elementos del lenguaje visual.</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>Analizar</t>
-        </is>
-      </c>
-      <c r="G11" s="5" t="inlineStr">
-        <is>
-          <t>• Exponen trabajos de arte, comunicando sus preferencias.
-• Hablan de los trabajos que más les gustan.
-• Describen trabajos de arte en relación con: - las emociones y sensaciones que transmiten - la aplicación de tipos de líneas con diferentes propósitos expresivos
-• Respetan los comentarios que hacen sus compañeros de trabajos de arte.
-• Describen trabajos de arte, considerando: - situaciones, paisajes y objetos en trabajos de arte - el uso de colores puros y mezclados con diferentes propósitos expresivos
-• Describen elementos originales en sus trabajos.
-• Explican preferencias frente a trabajos de arte con relación al uso del color.
-• Seleccionan, ayudados por el profesor, trabajos de arte para ser expuestos en el establecimiento o en la página web.
-• Reconocen y describen el uso de líneas, colores (fríos y cálidos) y texturas (visuales y táctiles) en su trabajo de arte personal y en el de sus pares.
-• Describen las emociones e historias expresadas por sus compañeros en trabajos de arte.
-• Respetan los trabajos de arte personales y de otros y la selección que hacen sus compañeros de estos.
-• Explican preferencias frente a trabajos de arte personal y de sus pares.</t>
-        </is>
-      </c>
-    </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
@@ -1013,6 +1015,58 @@
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>• Describen observaciones de imágenes y obras de arte de personas, del entorno, de otros ámbitos y paisajes chilenos.
+• Expresan emociones e ideas por medio de esculturas y collages, entre otros, con los temas de personas.
+• Crean pinturas, esculturas y collages expresivas con el tema de personas, del entorno, de otros ámbitos y paisajes chilenos.
+• Desarrollan ideas para sus trabajos personales basados en la observación de imágenes, obras de arte, experiencias personales e imaginación.
+• Identifican características personales y aspectos de su propia identidad y las expresan en pinturas y esculturas.
+• Describen observaciones de imágenes y de obras de arte con temas patrimoniales, y de figura humana.
+• Seleccionan entre materiales dados por el profesor para desarrollar sus trabajos de arte.
+• Expresan emociones e ideas en pinturas y collages con el tema del retrato (persona, familiar y colectivo).
+• Crean pinturas, esculturas y collages con el tema de: - retrato y autorretrato - patrimonio cultural de Chile
+• Describen observaciones de obras de arte con temas de paisajes chilenos y figura humana.
+• Pintan basados en la observación de obras de arte y fotografías de personajes de diferentes épocas y culturas.
+• Realizan pinturas y esculturas con temas personales y basadas en la observación de obras de arte y fotografías con temas de paisajes chilenos y figura humana.
+• Expresan emociones e ideas por medio de pinturas y esculturas con los temas de figura humana y paisaje chileno.
+• Desarrollan ideas para sus trabajos de arte, basándose en la música, experiencias, historias e imaginación.
+• Pintan creativamente, basados en la observación de fotografías y obras de arte de diferentes épocas y culturas acerca de personas.
+• Realizan trabajos de arte, basados en temas personales y en temas contingentes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>2° Básico</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>Expresar y crear visualmente</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>OA 1</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="inlineStr">
+        <is>
+          <t>Expresar y crear trabajos de arte a partir de la observación del: › entorno natural: figura humana y paisajes chilenos › entorno cultural: personas y patrimonio cultural de Chile › entorno artístico: obras de arte local, chileno, latinoamericano y del resto del mundo</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>• Describen observaciones de imágenes y obras de arte de personas, del entorno, de otros ámbitos y paisajes chilenos.
 • Expresan emociones e ideas por medio de esculturas y collages, entre otros, con los temas de personas.
@@ -1033,38 +1087,38 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>2° Básico</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Expresar y crear visualmente</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>OA 2</t>
         </is>
       </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>Experimentar y aplicar elementos del lenguaje visual (incluidos los del nivel anterior) en sus trabajos de arte: › línea (vertical, horizontal, diagonal, espiral y quebrada) › color (primarios y secundarios) › formas (geométricas)</t>
         </is>
       </c>
-      <c r="F13" s="4" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Aplicar</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>• Identifican y dan ejemplos de colores primarios, secundarios y formas geométricas en su entorno y en obras de arte.
 • Experimentan con diferentes procedimientos y materiales para obtener nuevos colores.
@@ -1079,38 +1133,134 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>2° Básico</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C14" s="3" t="inlineStr">
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Expresar y crear visualmente</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>OA 2</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>Experimentar y aplicar elementos del lenguaje visual (incluidos los del nivel anterior) en sus trabajos de arte: › línea (vertical, horizontal, diagonal, espiral y quebrada) › color (primarios y secundarios) › formas (geométricas)</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>Aplicar</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>• Identifican y dan ejemplos de colores primarios, secundarios y formas geométricas en su entorno y en obras de arte.
+• Experimentan con diferentes procedimientos y materiales para obtener nuevos colores.
+• Aplican colores primarios y secundarios en sus trabajos de arte, usando diferentes materiales (por ejemplo: papel crepé, de volantín, témperas, entre otros).
+• Aplican distintas formas geométricas en sus trabajos de arte.
+• Aplican elementos de lenguaje visual en sus trabajos para expresar emociones.
+• Identifican diversos tipos de líneas y formas geométricas en el entorno y en obras de arte.
+• Experimentan con diferentes tipos de líneas y formas geométricas en sus trabajos de arte.
+• Aplican diferentes tipos de líneas y formas geométricas en sus trabajos de arte en forma intencionada.
+• Aplican diferentes tipos de líneas y formas geométricas en sus trabajos de arte para expresar emociones e ideas.
+• Realizan dibujos digitales, usando diferentes tipos de líneas y formas geométricas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2° Básico</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Expresar y crear visualmente</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>OA 3</t>
         </is>
       </c>
-      <c r="E14" s="3" t="inlineStr">
+      <c r="E16" s="3" t="inlineStr">
         <is>
           <t>Expresar emociones e ideas en sus trabajos de arte, a partir de la experimentación con: › materiales de modelado, de reciclaje, naturales, papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales › herramientas para dibujar, pintar, cortar, modelar, unir y tecnológicas (pincel, tijera, mirete, computador, entre otras) › procedimientos de dibujo, pintura, collage, escultura, dibujo digital, entre otros</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>• Experimentan y usan variados procedimientos técnicos en pintura, escultura y relieve para crear trabajos de arte.
+• Proponen formas innovadoras para aplicar diferentes materiales, herramientas y procedimientos.
+• Usan diferentes materiales y herramientas para realizar collages y esculturas. (papel crepé, volantín, greda, arcilla, cartón, papel aluminio, cola fría, entre otros).
+• Expresan emociones, ideas y su propia imaginación por medio de collages y esculturas.
+• Experimentan y usan diferentes materiales y herramientas para realizar pinturas, collages y esculturas (pasteles grasos, tintas, témpera, elementos naturales, material de reciclaje, globos, entre otros).
+• Expresan emociones, ideas y su propia imaginación en pinturas, collages y esculturas.
+• Desarrollan ideas para sus trabajos personales, basados en la observación de imágenes, obras de arte, experiencias personales e imaginación.
+• Crean pinturas y esculturas a partir de la experimentación con materiales y procedimientos.
+• Usan diferentes materiales y herramientas para realizar pinturas, y esculturas (lápices de cera, pasteles grasos, témpera, plasticina, material de reciclaje, entre otros).
+• Expresan emociones, ideas y su propia imaginación en sus trabajos de arte acerca de experiencias y temas personales.
+• Experimentan y usan distintos procedimientos, materiales y herramientas en sus trabajos de arte.
+• Crean pinturas a partir de la música.
+• Crean títeres y juegos dramáticos visuales a partir de diferentes motivaciones.
+• Expresan emociones, ideas y su propia imaginación en trabajos de arte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>2° Básico</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Expresar y crear visualmente</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>OA 3</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="inlineStr">
+        <is>
+          <t>Expresar emociones e ideas en sus trabajos de arte, a partir de la experimentación con: › materiales de modelado, de reciclaje, naturales, papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales › herramientas para dibujar, pintar, cortar, modelar, unir y tecnológicas (pincel, tijera, mirete, computador, entre otras) › procedimientos de dibujo, pintura, collage, escultura, dibujo digital, entre otros</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>• Experimentan y usan variados procedimientos técnicos en pintura, escultura y relieve para crear trabajos de arte.
 • Proponen formas innovadoras para aplicar diferentes materiales, herramientas y procedimientos.
@@ -1130,38 +1280,87 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>2° Básico</t>
         </is>
       </c>
-      <c r="B15" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C15" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>Apreciar y responder frente al arte</t>
         </is>
       </c>
-      <c r="D15" s="4" t="inlineStr">
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>OA 4</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr">
+      <c r="E18" s="3" t="inlineStr">
         <is>
           <t>Comunicar y explicar sus impresiones de lo que sienten y piensan de obras de arte por variados medios. (Observar anualmente al menos 10 obras de arte local o chileno, 10 latinoamericanas y 10 de arte universal).</t>
         </is>
       </c>
-      <c r="F15" s="4" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Comprender</t>
         </is>
       </c>
-      <c r="G15" s="5" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>• Comunican oralmente, por escrito o usando la expresión corporal, lo que sienten (sentimientos y emociones) y piensan de las obras de arte.
+• Explican sus impresiones de las obras de arte oralmente o usando la expresión corporal.
+• Observan y describen en las obras de arte: - los elementos (forma y colores) y objetos que contienen - las escenas, personajes y temas - sus aspectos originales y posibles significados
+• Observan y describen escenas, personajes y temas de retratos y paisajes de Chile.
+• Describen materiales usados en obras de arte.
+• Describen sus impresiones sobre obras de arte.
+• Describen líneas, colores y formas presentes en retratos y paisajes de Chile.
+• Establecen relaciones entre colores y sentimientos.
+• Comunican sus sensaciones e impresiones acerca de obras de arte, usando diferentes medios (lenguaje oral y escrito).
+• Comunican lo que sienten y piensan de obras de arte, por escrito o usando la expresión corporal.
+• Describen escenas, personajes y temas de diferentes obras de arte.
+• Describen sus impresiones reflejadas en obras de arte.
+• Describen líneas, colores y formas presentes en las obras de arte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>2° Básico</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Apreciar y responder frente al arte</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>OA 4</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>Comunicar y explicar sus impresiones de lo que sienten y piensan de obras de arte por variados medios. (Observar anualmente al menos 10 obras de arte local o chileno, 10 latinoamericanas y 10 de arte universal).</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>Comprender</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>• Comunican oralmente, por escrito o usando la expresión corporal, lo que sienten (sentimientos y emociones) y piensan de las obras de arte.
 • Explican sus impresiones de las obras de arte oralmente o usando la expresión corporal.
@@ -1178,38 +1377,86 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>2° Básico</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C16" s="3" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
         <is>
           <t>Apreciar y responder frente al arte</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>OA 5</t>
         </is>
       </c>
-      <c r="E16" s="3" t="inlineStr">
+      <c r="E20" s="3" t="inlineStr">
         <is>
           <t>Explicar sus preferencias frente al trabajo de arte personal y de sus pares, usando elementos del lenguaje visual.</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Comprender</t>
         </is>
       </c>
-      <c r="G16" s="3" t="inlineStr">
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>• Describen las emociones personales frente a su trabajo de arte y el de sus compañeros.
+• Comunican sus preferencias frente al trabajo personal y de otros, usando la expresión oral y corporal.
+• Explican cómo aplicaron los elementos de lenguaje visual en sus trabajos de arte y el de sus compañeros.
+• Respetan los comentarios y preferencias que hacen sus compañeros de trabajos de arte.
+• Comparan trabajos en relación con las emociones que estos generan.
+• Comparan trabajos de arte, usando criterios relacionados con la aplicación de lenguaje visual.
+• Reconocen y explican la aplicación de elementos de lenguaje visual en su trabajo y en el de sus pares.
+• Explican significados del trabajo personal.
+• Exponen y hablan de sus trabajos de arte, comunicando sus preferencias.
+• Explican preferencias frente a trabajos de arte, usando como criterio la originalidad en el uso de materiales, formas y colores.
+• Infieren significados de trabajos de arte de sus compañeros.
+• Seleccionan trabajos de arte ayudados por el profesor para ser expuestos en el establecimiento o en la página web.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>2° Básico</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Apreciar y responder frente al arte</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>OA 5</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr">
+        <is>
+          <t>Explicar sus preferencias frente al trabajo de arte personal y de sus pares, usando elementos del lenguaje visual.</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>Comprender</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>• Describen las emociones personales frente a su trabajo de arte y el de sus compañeros.
 • Comunican sus preferencias frente al trabajo personal y de otros, usando la expresión oral y corporal.
@@ -1230,251 +1477,6 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="4" t="inlineStr">
-        <is>
-          <t>2° Básico</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C17" s="5" t="inlineStr">
-        <is>
-          <t>Expresar y crear visualmente</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>OA 1</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr">
-        <is>
-          <t>Expresar y crear trabajos de arte a partir de la observación del: › entorno natural: figura humana y paisajes chilenos › entorno cultural: personas y patrimonio cultural de Chile › entorno artístico: obras de arte local, chileno, latinoamericano y del resto del mundo</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr">
-        <is>
-          <t>• Describen observaciones de imágenes y obras de arte de personas, del entorno, de otros ámbitos y paisajes chilenos.
-• Expresan emociones e ideas por medio de esculturas y collages, entre otros, con los temas de personas.
-• Crean pinturas, esculturas y collages expresivas con el tema de personas, del entorno, de otros ámbitos y paisajes chilenos.
-• Desarrollan ideas para sus trabajos personales basados en la observación de imágenes, obras de arte, experiencias personales e imaginación.
-• Identifican características personales y aspectos de su propia identidad y las expresan en pinturas y esculturas.
-• Describen observaciones de imágenes y de obras de arte con temas patrimoniales, y de figura humana.
-• Seleccionan entre materiales dados por el profesor para desarrollar sus trabajos de arte.
-• Expresan emociones e ideas en pinturas y collages con el tema del retrato (persona, familiar y colectivo).
-• Crean pinturas, esculturas y collages con el tema de: - retrato y autorretrato - patrimonio cultural de Chile
-• Describen observaciones de obras de arte con temas de paisajes chilenos y figura humana.
-• Pintan basados en la observación de obras de arte y fotografías de personajes de diferentes épocas y culturas.
-• Realizan pinturas y esculturas con temas personales y basadas en la observación de obras de arte y fotografías con temas de paisajes chilenos y figura humana.
-• Expresan emociones e ideas por medio de pinturas y esculturas con los temas de figura humana y paisaje chileno.
-• Desarrollan ideas para sus trabajos de arte, basándose en la música, experiencias, historias e imaginación.
-• Pintan creativamente, basados en la observación de fotografías y obras de arte de diferentes épocas y culturas acerca de personas.
-• Realizan trabajos de arte, basados en temas personales y en temas contingentes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>2° Básico</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C18" s="3" t="inlineStr">
-        <is>
-          <t>Expresar y crear visualmente</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>OA 2</t>
-        </is>
-      </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t>Experimentar y aplicar elementos del lenguaje visual (incluidos los del nivel anterior) en sus trabajos de arte: › línea (vertical, horizontal, diagonal, espiral y quebrada) › color (primarios y secundarios) › formas (geométricas)</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Aplicar</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t>• Identifican y dan ejemplos de colores primarios, secundarios y formas geométricas en su entorno y en obras de arte.
-• Experimentan con diferentes procedimientos y materiales para obtener nuevos colores.
-• Aplican colores primarios y secundarios en sus trabajos de arte, usando diferentes materiales (por ejemplo: papel crepé, de volantín, témperas, entre otros).
-• Aplican distintas formas geométricas en sus trabajos de arte.
-• Aplican elementos de lenguaje visual en sus trabajos para expresar emociones.
-• Identifican diversos tipos de líneas y formas geométricas en el entorno y en obras de arte.
-• Experimentan con diferentes tipos de líneas y formas geométricas en sus trabajos de arte.
-• Aplican diferentes tipos de líneas y formas geométricas en sus trabajos de arte en forma intencionada.
-• Aplican diferentes tipos de líneas y formas geométricas en sus trabajos de arte para expresar emociones e ideas.
-• Realizan dibujos digitales, usando diferentes tipos de líneas y formas geométricas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="4" t="inlineStr">
-        <is>
-          <t>2° Básico</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C19" s="5" t="inlineStr">
-        <is>
-          <t>Expresar y crear visualmente</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>OA 3</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr">
-        <is>
-          <t>Expresar emociones e ideas en sus trabajos de arte, a partir de la experimentación con: › materiales de modelado, de reciclaje, naturales, papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales › herramientas para dibujar, pintar, cortar, modelar, unir y tecnológicas (pincel, tijera, mirete, computador, entre otras) › procedimientos de dibujo, pintura, collage, escultura, dibujo digital, entre otros</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr">
-        <is>
-          <t>• Experimentan y usan variados procedimientos técnicos en pintura, escultura y relieve para crear trabajos de arte.
-• Proponen formas innovadoras para aplicar diferentes materiales, herramientas y procedimientos.
-• Usan diferentes materiales y herramientas para realizar collages y esculturas. (papel crepé, volantín, greda, arcilla, cartón, papel aluminio, cola fría, entre otros).
-• Expresan emociones, ideas y su propia imaginación por medio de collages y esculturas.
-• Experimentan y usan diferentes materiales y herramientas para realizar pinturas, collages y esculturas (pasteles grasos, tintas, témpera, elementos naturales, material de reciclaje, globos, entre otros).
-• Expresan emociones, ideas y su propia imaginación en pinturas, collages y esculturas.
-• Desarrollan ideas para sus trabajos personales, basados en la observación de imágenes, obras de arte, experiencias personales e imaginación.
-• Crean pinturas y esculturas a partir de la experimentación con materiales y procedimientos.
-• Usan diferentes materiales y herramientas para realizar pinturas, y esculturas (lápices de cera, pasteles grasos, témpera, plasticina, material de reciclaje, entre otros).
-• Expresan emociones, ideas y su propia imaginación en sus trabajos de arte acerca de experiencias y temas personales.
-• Experimentan y usan distintos procedimientos, materiales y herramientas en sus trabajos de arte.
-• Crean pinturas a partir de la música.
-• Crean títeres y juegos dramáticos visuales a partir de diferentes motivaciones.
-• Expresan emociones, ideas y su propia imaginación en trabajos de arte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>2° Básico</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C20" s="3" t="inlineStr">
-        <is>
-          <t>Apreciar y responder frente al arte</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>OA 4</t>
-        </is>
-      </c>
-      <c r="E20" s="3" t="inlineStr">
-        <is>
-          <t>Comunicar y explicar sus impresiones de lo que sienten y piensan de obras de arte por variados medios. (Observar anualmente al menos 10 obras de arte local o chileno, 10 latinoamericanas y 10 de arte universal).</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Comprender</t>
-        </is>
-      </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t>• Comunican oralmente, por escrito o usando la expresión corporal, lo que sienten (sentimientos y emociones) y piensan de las obras de arte.
-• Explican sus impresiones de las obras de arte oralmente o usando la expresión corporal.
-• Observan y describen en las obras de arte: - los elementos (forma y colores) y objetos que contienen - las escenas, personajes y temas - sus aspectos originales y posibles significados
-• Observan y describen escenas, personajes y temas de retratos y paisajes de Chile.
-• Describen materiales usados en obras de arte.
-• Describen sus impresiones sobre obras de arte.
-• Describen líneas, colores y formas presentes en retratos y paisajes de Chile.
-• Establecen relaciones entre colores y sentimientos.
-• Comunican sus sensaciones e impresiones acerca de obras de arte, usando diferentes medios (lenguaje oral y escrito).
-• Comunican lo que sienten y piensan de obras de arte, por escrito o usando la expresión corporal.
-• Describen escenas, personajes y temas de diferentes obras de arte.
-• Describen sus impresiones reflejadas en obras de arte.
-• Describen líneas, colores y formas presentes en las obras de arte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>2° Básico</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C21" s="5" t="inlineStr">
-        <is>
-          <t>Apreciar y responder frente al arte</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>OA 5</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr">
-        <is>
-          <t>Explicar sus preferencias frente al trabajo de arte personal y de sus pares, usando elementos del lenguaje visual.</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
-          <t>Comprender</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr">
-        <is>
-          <t>• Describen las emociones personales frente a su trabajo de arte y el de sus compañeros.
-• Comunican sus preferencias frente al trabajo personal y de otros, usando la expresión oral y corporal.
-• Explican cómo aplicaron los elementos de lenguaje visual en sus trabajos de arte y el de sus compañeros.
-• Respetan los comentarios y preferencias que hacen sus compañeros de trabajos de arte.
-• Comparan trabajos en relación con las emociones que estos generan.
-• Comparan trabajos de arte, usando criterios relacionados con la aplicación de lenguaje visual.
-• Reconocen y explican la aplicación de elementos de lenguaje visual en su trabajo y en el de sus pares.
-• Explican significados del trabajo personal.
-• Exponen y hablan de sus trabajos de arte, comunicando sus preferencias.
-• Explican preferencias frente a trabajos de arte, usando como criterio la originalidad en el uso de materiales, formas y colores.
-• Infieren significados de trabajos de arte de sus compañeros.
-• Seleccionan trabajos de arte ayudados por el profesor para ser expuestos en el establecimiento o en la página web.</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
@@ -1488,25 +1490,75 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
+          <t>EXPRESAR Y CREAR VISUALMENTE</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>OA 1</t>
+        </is>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>Crear trabajos de arte con un propósito expresivo personal y basados en la observación del: entorno natural: animales, plantas y fenómenos naturales; entorno cultural: creencias de distintas culturas (mitos, seres imaginarios, dioses, fiestas, tradiciones, otros); entorno artístico: arte de la Antigüedad y movimientos artísticos como fauvismo, expresionismo y art nouveau</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G22" s="3" t="inlineStr">
+        <is>
+          <t>• Describen observaciones de animales, plantas, flores, árboles, insectos, paisajes del entorno natural y fenómenos naturales.
+• Elaboran bocetos para desarrollar ideas para sus trabajos de arte, basados en su imaginación y la observación de animales, plantas y fenómenos naturales.
+• Seleccionan materiales para la creación de sus trabajos de arte en relación con el propósito expresivo.
+• Registran observaciones directas de animales, plantas y de la naturaleza por medio del dibujo o la fotografía.
+• Realizan trabajos de arte creativos: usando procedimientos de pintura, escultura y técnicas mixtas, con los temas de animales, plantas del entorno natural y fenómenos de la naturaleza, usando diferentes materiales.
+• Describen observaciones de imágenes de personajes y seres imaginarios observados en ilustraciones, obras de arte y objetos de artesanía.
+• Elaboran bocetos para desarrollar ideas para sus trabajos de arte, basados en su imaginación y la observación de seres imaginarios en obras de arte, películas y objetos artesanales.
+• Realizan creativamente esculturas de personajes y seres imaginarios.
+• Usan creativamente técnicas mixtas en sus trabajos de arte acerca de personajes y seres imaginarios.
+• Crean juegos, presentaciones de teatro de sombras, máscaras y otros elementos con el tema de seres imaginarios.
+• Describen observaciones de personajes y seres imaginarios presentes en obras de arte y objetos de artesanía de diferentes épocas y culturas.
+• Pintan, realizan esculturas y objetos de artesanía basados en: la observación de obras de arte de personajes y seres imaginarios de diferentes épocas y culturas, cuentos, narraciones y leyendas acerca de personajes y seres imaginarios.
+• Describen observaciones de obras de arte y artesanía de las culturas de la Antigüedad y de los movimientos fauvista, expresionista y art nouveau.
+• Realizan fotografías, grabados, pinturas y esculturas basados en la observación de obras de arte y artesanía de las culturas de la Antigüedad y de los movimientos fauvistas, expresionistas y art nouveau.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>3° Básico</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
           <t>Expresar y crear visualmente</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D23" s="4" t="inlineStr">
         <is>
           <t>OA 1</t>
         </is>
       </c>
-      <c r="E22" s="3" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Crear trabajos de arte con un propósito expresivo personal y basados en la observación del: entorno natural: animales, plantas y fenómenos naturales; entorno cultural: creencias de distintas culturas (mitos, seres imaginarios, dioses, fiestas, tradiciones, otros); entorno artístico: arte de la Antigüedad y movimientos artísticos como fauvismo, expresionismo y art nouveau</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>• Describen observaciones de animales, plantas, flores, árboles, insectos, paisajes del entorno natural y fenómenos naturales.
 • Elaboran bocetos para desarrollar ideas para sus trabajos de arte, basados en su imaginación y la observación de animales, plantas y fenómenos naturales.
@@ -1525,38 +1577,38 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>3° Básico</t>
         </is>
       </c>
-      <c r="B23" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C23" s="5" t="inlineStr">
-        <is>
-          <t>Expresar y crear visualmente</t>
-        </is>
-      </c>
-      <c r="D23" s="4" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>EXPRESAR Y CREAR VISUALMENTE</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>OA 2</t>
         </is>
       </c>
-      <c r="E23" s="5" t="inlineStr">
+      <c r="E24" s="3" t="inlineStr">
         <is>
           <t>Aplicar elementos del lenguaje visual (incluidos los de niveles anteriores) en sus trabajos de arte, con diversos propósitos expresivos y creativos: color (frío, cálido y expresivo); textura (en plano y volumen); forma (real y recreada)</t>
         </is>
       </c>
-      <c r="F23" s="4" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Aplicar</t>
         </is>
       </c>
-      <c r="G23" s="5" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>• Reconocen formas reales y recreadas en obras de arte, artesanía, cine y otros.
 • Pintan creativamente, usando técnicas mixtas de acuerdo con un propósito expresivo usando formas reales y/o recreadas.
@@ -1569,38 +1621,82 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>3° Básico</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C24" s="3" t="inlineStr">
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>Expresar y crear visualmente</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>OA 2</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>Aplicar elementos del lenguaje visual (incluidos los de niveles anteriores) en sus trabajos de arte, con diversos propósitos expresivos y creativos: color (frío, cálido y expresivo); textura (en plano y volumen); forma (real y recreada)</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>Aplicar</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>• Reconocen formas reales y recreadas en obras de arte, artesanía, cine y otros.
+• Pintan creativamente, usando técnicas mixtas de acuerdo con un propósito expresivo usando formas reales y/o recreadas.
+• Realizan trabajos de arte con un propósito expresivo, usando formas reales y/o recreadas.
+• Reconocen y describen sensaciones de texturas táctiles y visuales.
+• Realizan pinturas, esculturas creativas y objetos de artesanía con un propósito expresivo, usando texturas táctiles y visuales.
+• Reconocen colores fríos, cálidos y expresivos, y los aplican en sus trabajos de arte para expresar emociones y sensaciones.
+• Experimentan con diversos procedimientos de pintura, grabado y fotografía.
+• Utilizan variados materiales para realizar sus trabajos de arte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>3° Básico</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>EXPRESAR Y CREAR VISUALMENTE</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>OA 3</t>
         </is>
       </c>
-      <c r="E24" s="3" t="inlineStr">
-        <is>
-          <t>Crear trabajos de arte a partir de experiencias, intereses y temas del entorno natural y artístico, demostrando manejo de: materiales de modelado, de reciclaje, naturales, papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales; herramientas para dibujar, pintar, cortar, modelar, unir y tecnológicas (pincel, tijera, mirete, computador, cámara fotográfica, entre otras); procedimientos de dibujo, pintura, grabado, escultura, técnicas mixtas, artesanía, fotografía, entre otros</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
+        <is>
+          <t>Crear trabajos de arte a partir de experiencias, intereses y temas del entorno natural y artístico, demostrando manejo de: materiales de modelado, de reciclaje, naturales papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales; herramientas para dibujar, pintar, cortar, modelar unir y tecnológicas (pincel, tijera, mirete, computador, cámara fotográfica, entre otras); procedimientos de dibujo, pintura, grabado, escultura, técnicas mixtas, artesanía, fotografía, entre otros</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G26" s="3" t="inlineStr">
         <is>
           <t>• Experimentan con diversos procedimientos de pintura, escultura y técnicas mixtas.
 • Explican preferencias por determinados materiales, herramientas y procedimientos creativos.
@@ -1619,98 +1715,6 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>3° Básico</t>
-        </is>
-      </c>
-      <c r="B25" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C25" s="5" t="inlineStr">
-        <is>
-          <t>Apreciar y responder frente al arte</t>
-        </is>
-      </c>
-      <c r="D25" s="4" t="inlineStr">
-        <is>
-          <t>OA 4</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>Describir sus observaciones de obras de arte y objetos, usando elementos del lenguaje visual y expresando lo que sienten y piensan. (Observar anualmente al menos 15 obras de arte y artesanía local y chilena, 15 latinoamericanas y 15 de arte universal).</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
-          <t>Comprender</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>• Describen diferentes colores, texturas, tamaños, figuras y formas de plantas, animales y fenómenos naturales.
-• Describen temas y materiales utilizados en obras de arte sobre la naturaleza.
-• Describen elementos del lenguaje visual contenidos en las obras y objetos observados.
-• Comunican lo que sienten al observar obras de arte, películas y objetos de artesanía.
-• Describen materiales usados en obras de arte, ilustraciones y objetos de artesanía.
-• Describen temas de diferentes obras de arte, ilustraciones, cine, cuentos y objetos de artesanía.
-• Describen colores, formas y texturas presentes en las obras de arte, ilustraciones y objetos de artesanía, utilizando elementos de lenguaje visual.
-• Describen emociones e ideas personales basadas en la observación de obras de arte de la Antigüedad.
-• Describen obras de arte y objetos de artesanía de la Antigüedad en relación con: escenas y personajes representados; la utilización de materiales y procedimientos; uso del lenguaje visual.
-• Comparan obras de arte y objetos de artesanía en relación con su temática y uso de elementos de lenguaje visual.
-• Describen sentimientos e ideas personales basadas en la observación de obras del arte de la Antigüedad y los movimientos fauvista, expresionista y art nouveau.
-• Describen obras de arte de la Antigüedad y de los movimientos fauvista, expresionista y art nouveau, identificando: temas, escena y personajes; materiales y procedimientos; el uso del lenguaje visual (línea,color, forma, textura u otros).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>3° Básico</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C26" s="3" t="inlineStr">
-        <is>
-          <t>Apreciar y responder frente al arte</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>OA 5</t>
-        </is>
-      </c>
-      <c r="E26" s="3" t="inlineStr">
-        <is>
-          <t>Describir fortalezas y aspectos a mejorar en el trabajo de arte personal y de sus pares, usando criterios de uso de materiales, procedimientos técnicos y propósito expresivo.</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Comprender</t>
-        </is>
-      </c>
-      <c r="G26" s="3" t="inlineStr">
-        <is>
-          <t>• Exponen y hablan de sus trabajos de arte y objetos artesanales: usando adecuadamente el vocabulario y términos de lenguaje visual; proponiendo ideas para mejorar trabajos personales y de sus compañeros; respetando a sus compañeros.
-• Explican y justifican el uso de materiales, procedimientos y la aplicación de elementos de lenguaje visual en el trabajo de arte personal.
-• Describen fortalezas y debilidades de sus trabajos de arte y de los compañeros en relación con la aplicación de elementos de lenguaje visual y sus propósitos expresivos.
-• Exponen sus trabajos de arte y objetos artesanales, justificando el uso de materiales, procedimientos y la aplicación de elementos de lenguaje visual.
-• Describen y comparan fortalezas y debilidades de trabajos de arte personales y de otros con respecto a la utilización de materiales, procedimientos y la aplicación de elementos de lenguaje visual.
-• Proponen ideas para mejorar trabajos personales y de sus compañeros de manera respetuosa.
-• Usan adecuadamente el vocabulario y términos de lenguaje visual.
-• Seleccionan trabajos de arte ayudados por el profesor para ser expuestos en el establecimiento o en la página web.</t>
-        </is>
-      </c>
-    </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
@@ -1719,22 +1723,22 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>EXPRESAR Y CREAR VISUALMENTE</t>
+          <t>Expresar y crear visualmente</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>OA 1</t>
+          <t>OA 3</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>Crear trabajos de arte con un propósito expresivo personal y basados en la observación del: entorno natural: animales, plantas y fenómenos naturales; entorno cultural: creencias de distintas culturas (mitos, seres imaginarios, dioses, fiestas, tradiciones, otros); entorno artístico: arte de la Antigüedad y movimientos artísticos como fauvismo, expresionismo y art nouveau</t>
+          <t>Crear trabajos de arte a partir de experiencias, intereses y temas del entorno natural y artístico, demostrando manejo de: materiales de modelado, de reciclaje, naturales, papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales; herramientas para dibujar, pintar, cortar, modelar, unir y tecnológicas (pincel, tijera, mirete, computador, cámara fotográfica, entre otras); procedimientos de dibujo, pintura, grabado, escultura, técnicas mixtas, artesanía, fotografía, entre otros</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -1743,100 +1747,6 @@
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
-        <is>
-          <t>• Describen observaciones de animales, plantas, flores, árboles, insectos, paisajes del entorno natural y fenómenos naturales.
-• Elaboran bocetos para desarrollar ideas para sus trabajos de arte, basados en su imaginación y la observación de animales, plantas y fenómenos naturales.
-• Seleccionan materiales para la creación de sus trabajos de arte en relación con el propósito expresivo.
-• Registran observaciones directas de animales, plantas y de la naturaleza por medio del dibujo o la fotografía.
-• Realizan trabajos de arte creativos: usando procedimientos de pintura, escultura y técnicas mixtas, con los temas de animales, plantas del entorno natural y fenómenos de la naturaleza, usando diferentes materiales.
-• Describen observaciones de imágenes de personajes y seres imaginarios observados en ilustraciones, obras de arte y objetos de artesanía.
-• Elaboran bocetos para desarrollar ideas para sus trabajos de arte, basados en su imaginación y la observación de seres imaginarios en obras de arte, películas y objetos artesanales.
-• Realizan creativamente esculturas de personajes y seres imaginarios.
-• Usan creativamente técnicas mixtas en sus trabajos de arte acerca de personajes y seres imaginarios.
-• Crean juegos, presentaciones de teatro de sombras, máscaras y otros elementos con el tema de seres imaginarios.
-• Describen observaciones de personajes y seres imaginarios presentes en obras de arte y objetos de artesanía de diferentes épocas y culturas.
-• Pintan, realizan esculturas y objetos de artesanía basados en: la observación de obras de arte de personajes y seres imaginarios de diferentes épocas y culturas, cuentos, narraciones y leyendas acerca de personajes y seres imaginarios.
-• Describen observaciones de obras de arte y artesanía de las culturas de la Antigüedad y de los movimientos fauvista, expresionista y art nouveau.
-• Realizan fotografías, grabados, pinturas y esculturas basados en la observación de obras de arte y artesanía de las culturas de la Antigüedad y de los movimientos fauvistas, expresionistas y art nouveau.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>3° Básico</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>EXPRESAR Y CREAR VISUALMENTE</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>OA 2</t>
-        </is>
-      </c>
-      <c r="E28" s="3" t="inlineStr">
-        <is>
-          <t>Aplicar elementos del lenguaje visual (incluidos los de niveles anteriores) en sus trabajos de arte, con diversos propósitos expresivos y creativos: color (frío, cálido y expresivo); textura (en plano y volumen); forma (real y recreada)</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Aplicar</t>
-        </is>
-      </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t>• Reconocen formas reales y recreadas en obras de arte, artesanía, cine y otros.
-• Pintan creativamente, usando técnicas mixtas de acuerdo con un propósito expresivo usando formas reales y/o recreadas.
-• Realizan trabajos de arte con un propósito expresivo, usando formas reales y/o recreadas.
-• Reconocen y describen sensaciones de texturas táctiles y visuales.
-• Realizan pinturas, esculturas creativas y objetos de artesanía con un propósito expresivo, usando texturas táctiles y visuales.
-• Reconocen colores fríos, cálidos y expresivos, y los aplican en sus trabajos de arte para expresar emociones y sensaciones.
-• Experimentan con diversos procedimientos de pintura, grabado y fotografía.
-• Utilizan variados materiales para realizar sus trabajos de arte.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>3° Básico</t>
-        </is>
-      </c>
-      <c r="B29" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="inlineStr">
-        <is>
-          <t>EXPRESAR Y CREAR VISUALMENTE</t>
-        </is>
-      </c>
-      <c r="D29" s="4" t="inlineStr">
-        <is>
-          <t>OA 3</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="inlineStr">
-        <is>
-          <t>Crear trabajos de arte a partir de experiencias, intereses y temas del entorno natural y artístico, demostrando manejo de: materiales de modelado, de reciclaje, naturales papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales; herramientas para dibujar, pintar, cortar, modelar unir y tecnológicas (pincel, tijera, mirete, computador, cámara fotográfica, entre otras); procedimientos de dibujo, pintura, grabado, escultura, técnicas mixtas, artesanía, fotografía, entre otros</t>
-        </is>
-      </c>
-      <c r="F29" s="4" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G29" s="5" t="inlineStr">
         <is>
           <t>• Experimentan con diversos procedimientos de pintura, escultura y técnicas mixtas.
 • Explican preferencias por determinados materiales, herramientas y procedimientos creativos.
@@ -1855,38 +1765,38 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>3° Básico</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C30" s="3" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
         <is>
           <t>APRECIAR Y RESPONDER FRENTE AL ARTE</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>OA 4</t>
         </is>
       </c>
-      <c r="E30" s="3" t="inlineStr">
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>Describir sus observaciones de obras de arte y objetos, usando elementos del lenguaje visual y expresando lo que sienten y piensan. (Observar anualmente al menos 15 obras de arte y artesanía local y chilena, 15 latinoamericanas y 15 de arte universal).</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Comprender</t>
         </is>
       </c>
-      <c r="G30" s="3" t="inlineStr">
+      <c r="G28" s="3" t="inlineStr">
         <is>
           <t>• Describen diferentes colores, texturas, tamaños, figuras y formas de plantas, animales y fenómenos naturales.
 • Describen temas y materiales utilizados en obras de arte sobre la naturaleza.
@@ -1903,38 +1813,86 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>3° Básico</t>
         </is>
       </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C31" s="5" t="inlineStr">
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Apreciar y responder frente al arte</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>OA 4</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>Describir sus observaciones de obras de arte y objetos, usando elementos del lenguaje visual y expresando lo que sienten y piensan. (Observar anualmente al menos 15 obras de arte y artesanía local y chilena, 15 latinoamericanas y 15 de arte universal).</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Comprender</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>• Describen diferentes colores, texturas, tamaños, figuras y formas de plantas, animales y fenómenos naturales.
+• Describen temas y materiales utilizados en obras de arte sobre la naturaleza.
+• Describen elementos del lenguaje visual contenidos en las obras y objetos observados.
+• Comunican lo que sienten al observar obras de arte, películas y objetos de artesanía.
+• Describen materiales usados en obras de arte, ilustraciones y objetos de artesanía.
+• Describen temas de diferentes obras de arte, ilustraciones, cine, cuentos y objetos de artesanía.
+• Describen colores, formas y texturas presentes en las obras de arte, ilustraciones y objetos de artesanía, utilizando elementos de lenguaje visual.
+• Describen emociones e ideas personales basadas en la observación de obras de arte de la Antigüedad.
+• Describen obras de arte y objetos de artesanía de la Antigüedad en relación con: escenas y personajes representados; la utilización de materiales y procedimientos; uso del lenguaje visual.
+• Comparan obras de arte y objetos de artesanía en relación con su temática y uso de elementos de lenguaje visual.
+• Describen sentimientos e ideas personales basadas en la observación de obras del arte de la Antigüedad y los movimientos fauvista, expresionista y art nouveau.
+• Describen obras de arte de la Antigüedad y de los movimientos fauvista, expresionista y art nouveau, identificando: temas, escena y personajes; materiales y procedimientos; el uso del lenguaje visual (línea,color, forma, textura u otros).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>3° Básico</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
         <is>
           <t>APRECIAR Y RESPONDER FRENTE AL ARTE</t>
         </is>
       </c>
-      <c r="D31" s="4" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>OA 5</t>
         </is>
       </c>
-      <c r="E31" s="5" t="inlineStr">
+      <c r="E30" s="3" t="inlineStr">
         <is>
           <t>Describir fortalezas y aspectos a mejorar en el trabajo de arte personal y de sus pares, usando criterios de uso de materiales, procedimientos técnicos y propósito expresivo.</t>
         </is>
       </c>
-      <c r="F31" s="4" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Comprender</t>
         </is>
       </c>
-      <c r="G31" s="5" t="inlineStr">
+      <c r="G30" s="3" t="inlineStr">
         <is>
           <t>• Exponen y hablan de sus trabajos de arte y objetos artesanales: usando adecuadamente el vocabulario y términos de lenguaje visual, proponiendo ideas para mejorar trabajos personales y de sus compañeros, respetando a sus compañeros.
 • Explican y justifican el uso de materiales, procedimientos y la aplicación de elementos de lenguaje visual en el trabajo de arte personal.
@@ -1947,6 +1905,50 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>3° Básico</t>
+        </is>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Apreciar y responder frente al arte</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>OA 5</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>Describir fortalezas y aspectos a mejorar en el trabajo de arte personal y de sus pares, usando criterios de uso de materiales, procedimientos técnicos y propósito expresivo.</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="inlineStr">
+        <is>
+          <t>Comprender</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>• Exponen y hablan de sus trabajos de arte y objetos artesanales: usando adecuadamente el vocabulario y términos de lenguaje visual; proponiendo ideas para mejorar trabajos personales y de sus compañeros; respetando a sus compañeros.
+• Explican y justifican el uso de materiales, procedimientos y la aplicación de elementos de lenguaje visual en el trabajo de arte personal.
+• Describen fortalezas y debilidades de sus trabajos de arte y de los compañeros en relación con la aplicación de elementos de lenguaje visual y sus propósitos expresivos.
+• Exponen sus trabajos de arte y objetos artesanales, justificando el uso de materiales, procedimientos y la aplicación de elementos de lenguaje visual.
+• Describen y comparan fortalezas y debilidades de trabajos de arte personales y de otros con respecto a la utilización de materiales, procedimientos y la aplicación de elementos de lenguaje visual.
+• Proponen ideas para mejorar trabajos personales y de sus compañeros de manera respetuosa.
+• Usan adecuadamente el vocabulario y términos de lenguaje visual.
+• Seleccionan trabajos de arte ayudados por el profesor para ser expuestos en el establecimiento o en la página web.</t>
+        </is>
+      </c>
+    </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
@@ -1970,15 +1972,67 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
+          <t>Crear trabajos de arte con un propósito expresivo personal y basados en la observación del: › entorno natural: naturaleza y paisaje americano › entorno cultural: América y sus tradiciones (cultura precolombina, tradiciones y artesanía americana) › entorno artístico: arte precolombino y de movimientos artísticos como muralismo mexicano, naif y surrealismo en Chile, Latinoamérica y en el resto del mundo</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G32" s="3" t="inlineStr">
+        <is>
+          <t>• Participan en discusiones acerca de imágenes, videos y obras de arte sobre el entorno natural del paisaje americano.
+• Desarrollan ideas para sus trabajos por medio de la observación de imágenes y obras de arte acerca de fenómenos de la naturaleza.
+• Seleccionan obras de artistas con temas del entorno natural, el paisaje americano y Land Art como referentes para la creación personal.
+• Seleccionan adecuadamente materiales para la creación personal en relación con el propósito expresivo.
+• Crean pinturas y esculturas basadas en la expresión de emociones, experiencias e ideas acerca del entorno natural, el paisaje americano y Land Art.
+• Describen imágenes y objetos de artesanía del arte precolombino en relación con el tema y el uso de elementos de lenguaje visual.
+• Elaboran bocetos para desarrollar ideas para sus trabajos de arte.
+• Crean trabajos de arte de pintura y artesanía, basados en la observación de arte rupestre chileno, textiles, cerámica y máscaras del arte precolombino.
+• Describen imágenes y videos de obras y objetos de artesanía del arte precolombino americano en relación con temas y uso de elementos de lenguaje visual.
+• Desarrollan ideas para sus pinturas y esculturas por medio de bocetos.
+• Crean trabajos de arte de pintura y escultura basados en la observación de máscaras, murales, objetos de orfebrería y cerámica precolombina americana.
+• Describen y participan en discusiones acerca de imágenes y obras de arte naif, surrealistas y muralismo mexicano.
+• Desarrollan ideas por medio de bocetos para elaborar trabajos de arte de dibujo, pintura y escultura, basados en el arte naif, surrealistas y muralismo mexicano.
+• Crean trabajos de arte basados en la selección de obras de arte de los movimientos naif, surrealismo y muralismo mexicano como referentes para la creación personal.
+• Crean trabajos de arte basados en temas contingentes o de interés personal.
+• Crean dibujos, pinturas y murales, usando diferentes materiales, herramientas y procedimientos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>4° Básico</t>
+        </is>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Expresar y crear visualmente</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>OA 1</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
           <t>Crear trabajos de arte con un propósito expresivo personal y basados en la observación del: entorno natural: naturaleza y paisaje americano; entorno cultural: América y sus tradiciones (cultura precolombina, tradiciones y artesanía americana); entorno artístico: arte precolombino y de movimientos artísticos como muralismo mexicano, naif y surrealismo en Chile, Latinoamérica y en el resto del mundo.</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="4" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G32" s="3" t="inlineStr">
+      <c r="G33" s="5" t="inlineStr">
         <is>
           <t>• Participan en discusiones acerca de imágenes, videos y obras de arte sobre el entorno natural del paisaje americano.
 • Desarrollan ideas para sus trabajos por medio de la observación de imágenes y obras de arte acerca de fenómenos de la naturaleza.
@@ -1999,38 +2053,38 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>4° Básico</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C33" s="5" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
         <is>
           <t>Expresar y crear visualmente</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>OA 2</t>
         </is>
       </c>
-      <c r="E33" s="5" t="inlineStr">
-        <is>
-          <t>Aplicar elementos del lenguaje visual (incluidos los de niveles anteriores) en sus trabajos de arte, con diversos propósitos expresivos y creativos: líneas de contorno; color (tono y matiz); forma (figurativa y no figurativa).</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
+      <c r="E34" s="3" t="inlineStr">
+        <is>
+          <t>Aplicar elementos del lenguaje visual (incluidos los de niveles anteriores) en sus trabajos de arte, con diversos propósitos expresivos y creativos: › líneas de contorno › color (tono y matiz) › forma (figurativa y no figurativa)</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Aplicar</t>
         </is>
       </c>
-      <c r="G33" s="5" t="inlineStr">
+      <c r="G34" s="3" t="inlineStr">
         <is>
           <t>• Identifican y describen formas figurativas y no figurativas en obras de arte, pieles de animales e imágenes microscópicas, entre otros.
 • Aplican elementos del lenguaje visual en su trabajo de arte (formas figurativas y no figurativas) con distintos propósitos expresivos y creativos.
@@ -2045,38 +2099,136 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>4° Básico</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C34" s="3" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>Expresar y crear visualmente</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>OA 2</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>Aplicar elementos del lenguaje visual (incluidos los de niveles anteriores) en sus trabajos de arte, con diversos propósitos expresivos y creativos: líneas de contorno; color (tono y matiz); forma (figurativa y no figurativa).</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>Aplicar</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>• Identifican y describen formas figurativas y no figurativas en obras de arte, pieles de animales e imágenes microscópicas, entre otros.
+• Aplican elementos del lenguaje visual en su trabajo de arte (formas figurativas y no figurativas) con distintos propósitos expresivos y creativos.
+• Identifican y describen líneas de contorno en arte rupestre chileno y objetos de culturas precolombinas.
+• Elaboran pinturas y objetos de artesanía, aplicando conceptos del lenguaje visual, como línea de contorno.
+• Aplican elementos del lenguaje visual (línea de contorno) en su trabajo de arte con distintos propósitos expresivos.
+• Identifican y describen el uso de tonos y matices en la naturaleza y en obras del arte precolombino.
+• Experimentan con colores puros para obtener sus tonos y matices por medio de la pintura.
+• Crean trabajos de arte con distintos propósitos expresivos en forma libre y espontánea, aplicando conceptos del lenguaje visual como tonos y matices.
+• Identifican y describen formas figurativas y no figurativas en obras de arte.
+• Elaboran trabajos de arte, aplicando conceptos del lenguaje visual como forma figurativa y/o no figurativa y otros de los niveles anteriores.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>4° Básico</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr">
+        <is>
+          <t>Expresar y crear visualmente</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>OA 3</t>
         </is>
       </c>
-      <c r="E34" s="3" t="inlineStr">
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t>Crear trabajos de arte a partir de experiencias, intereses y temas del entorno natural, cultural y artístico, demostrando manejo de: › materiales de modelado, de reciclaje, naturales, papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales › herramientas para dibujar, pintar, cortar, unir, modelar y tecnológicas (pincel, tijera, mirete, computador, cámara fotográfica, entre otras) › procedimientos de dibujo, pintura, grabado, escultura, técnicas mixtas, artesanía, fotografía, entre otros</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t>• Experimentan e incorporan posibilidades de expresión con nuevos materiales y recursos de expresión visual.
+• Seleccionan y usan adecuadamente materiales, herramientas y procedimientos técnicos, explicando sus preferencias (por ejemplo: pasteles grasos, plumones, lápices acuarelables, témpera, acuarela, tintas, materiales naturales y de reciclaje, entre otros).
+• Crean esculturas y pinturas con temas relacionados con la naturaleza, el paisaje chileno, fenómenos de la naturaleza y temas personales.
+• Demuestran manejo de procedimientos de pintura y escultura (pintura con lápices o pinturas al agua, mosaico, escultura con materiales naturales, entre otros).
+• Crean pinturas y objetos de artesanía basados en la observación del arte precolombino e ideas personales.
+• Seleccionan adecuadamente materiales herramientas y procedimientos técnicos en relación con el propósito expresivo.
+• Explican preferencias por determinados materiales, herramientas y procedimientos.
+• Demuestran manejo de materiales como papeles, cartones, pinturas, material de reciclaje y natural, entre otros, y de herramientas como tijeras, pinceles, lápices, plumones, estecas, entre otras.
+• Demuestran manejo de procedimientos de pintura y artesanía (pintura con témpera, acrílico, técnicas mixtas y cerámica).
+• Experimentan e incorporan posibilidades de expresión con nuevos materiales y procedimientos en sus pinturas y objetos artesanales.
+• Seleccionan adecuadamente materiales, herramientas y procedimientos técnicos en relación con trabajos de arte u objeto de artesanía.
+• Explican preferencias por determinados materiales, herramientas y procedimientos creativos.
+• Crean esculturas y pinturas por medio de su imaginación y la observacion de diferentes obras y objetos de las culturas precolombinas.
+• Demuestran manejo de procedimientos de dibujo, pintura y escultura.
+• Demuestran manejo de materiales como papeles, cartones, pinturas, tintas y acuarelas, entre otros, y herramientas como tijeras, pinceles, lápices y plumones, entre otras.
+• Experimentan e incorporan nuevas posibilidades de expresión con distintos materiales y recursos de expresión visuales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>4° Básico</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Expresar y crear visualmente</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>OA 3</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
         <is>
           <t>Crear trabajos de arte a partir de experiencias, intereses y temas del entorno natural, cultural y artístico, demostrando manejo de: materiales de modelado, de reciclaje, naturales, papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales; herramientas para dibujar, pintar, cortar, unir, modelar y tecnológicas (pincel, tijera, mirete, computador, cámara fotográfica, entre otras); procedimientos de dibujo, pintura, grabado, escultura, técnicas mixtas, artesanía, fotografía, entre otros.</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F37" s="4" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G34" s="3" t="inlineStr">
+      <c r="G37" s="5" t="inlineStr">
         <is>
           <t>• Experimentan e incorporan posibilidades de expresión con nuevos materiales y recursos de expresión visual.
 • Seleccionan y usan adecuadamente materiales, herramientas y procedimientos técnicos, explicando sus preferencias (por ejemplo: pasteles grasos, plumones, lápices acuarelables, témpera, acuarela, tintas, materiales naturales y de reciclaje, entre otros).
@@ -2097,38 +2249,38 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>4° Básico</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C35" s="5" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C38" s="3" t="inlineStr">
         <is>
           <t>Apreciar y responder frente al arte</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>OA 4</t>
         </is>
       </c>
-      <c r="E35" s="5" t="inlineStr">
+      <c r="E38" s="3" t="inlineStr">
         <is>
           <t>Describir sus observaciones de obras de arte y objetos, usando elementos del lenguaje visual y expresando lo que sienten y piensan. (Observar anualmente al menos 15 obras de arte y artesanía local y chilena, 15 de arte latinoamericano y 15 de arte universal).</t>
         </is>
       </c>
-      <c r="F35" s="4" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Analizar</t>
         </is>
       </c>
-      <c r="G35" s="5" t="inlineStr">
+      <c r="G38" s="3" t="inlineStr">
         <is>
           <t>• Describen imágenes, videos y obras de arte sobre la naturaleza y el paisaje americano, usando elementos del lenguaje visual (línea, forma y color).
 • Reconocen y describen procedimientos de pintura, escultura y artesanía en obras de arte y objetos de artesanía.
@@ -2148,149 +2300,6 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>4° Básico</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C36" s="3" t="inlineStr">
-        <is>
-          <t>Apreciar y responder frente al arte</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>OA 5</t>
-        </is>
-      </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t>Describir fortalezas y aspectos a mejorar en el trabajo de arte personal y de sus pares, aplicando criterios de uso de materiales, procedimientos técnicos y propósito expresivo.</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>Analizar</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t>• Exponen y hablan de sus trabajos de arte y artesanía.
-• Describen los trabajos personales y de sus pares, resaltando fortalezas y aspectos a mejorar con respecto al uso de los materiales, procedimientos y aplicación de elementos de lenguaje visual.
-• Describen posibles significados, temas y emociones que transmiten sus trabajos personales y los de sus pares.
-• Comparan trabajos de arte, usando criterios relacionados con la aplicación de lenguaje visual.
-• Usan adecuadamente el vocabulario y términos de lenguaje visual (tipos de líneas, color, forma y textura).
-• Exponen y hablan de sus trabajos de arte y describen sus características y propósitos expresivos.
-• Describen y relacionan lo que han tratado de expresar y los resultados obtenidos en sus trabajos de arte (por ejemplo: usé colores cálidos para que la escena pareciera más alegre, usé líneas gruesas para darle más importancia al rostro).
-• Analizan y describen los trabajos personales y de sus pares, usando el vocabulario adecuado y resaltando fortalezas y aspectos e ideas a mejorar con respecto al uso de materiales, procedimientos técnicos y propósitos expresivos, de manera respetuosa.
-• Comparan trabajos de arte y los seleccionan, usando criterios relacionados con la aplicación de lenguaje visual y el propósito expresivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>4° Básico</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C37" s="5" t="inlineStr">
-        <is>
-          <t>Expresar y crear visualmente</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>OA 1</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="inlineStr">
-        <is>
-          <t>Crear trabajos de arte con un propósito expresivo personal y basados en la observación del: › entorno natural: naturaleza y paisaje americano › entorno cultural: América y sus tradiciones (cultura precolombina, tradiciones y artesanía americana) › entorno artístico: arte precolombino y de movimientos artísticos como muralismo mexicano, naif y surrealismo en Chile, Latinoamérica y en el resto del mundo</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G37" s="5" t="inlineStr">
-        <is>
-          <t>• Participan en discusiones acerca de imágenes, videos y obras de arte sobre el entorno natural del paisaje americano.
-• Desarrollan ideas para sus trabajos por medio de la observación de imágenes y obras de arte acerca de fenómenos de la naturaleza.
-• Seleccionan obras de artistas con temas del entorno natural, el paisaje americano y Land Art como referentes para la creación personal.
-• Seleccionan adecuadamente materiales para la creación personal en relación con el propósito expresivo.
-• Crean pinturas y esculturas basadas en la expresión de emociones, experiencias e ideas acerca del entorno natural, el paisaje americano y Land Art.
-• Describen imágenes y objetos de artesanía del arte precolombino en relación con el tema y el uso de elementos de lenguaje visual.
-• Elaboran bocetos para desarrollar ideas para sus trabajos de arte.
-• Crean trabajos de arte de pintura y artesanía, basados en la observación de arte rupestre chileno, textiles, cerámica y máscaras del arte precolombino.
-• Describen imágenes y videos de obras y objetos de artesanía del arte precolombino americano en relación con temas y uso de elementos de lenguaje visual.
-• Desarrollan ideas para sus pinturas y esculturas por medio de bocetos.
-• Crean trabajos de arte de pintura y escultura basados en la observación de máscaras, murales, objetos de orfebrería y cerámica precolombina americana.
-• Describen y participan en discusiones acerca de imágenes y obras de arte naif, surrealistas y muralismo mexicano.
-• Desarrollan ideas por medio de bocetos para elaborar trabajos de arte de dibujo, pintura y escultura, basados en el arte naif, surrealistas y muralismo mexicano.
-• Crean trabajos de arte basados en la selección de obras de arte de los movimientos naif, surrealismo y muralismo mexicano como referentes para la creación personal.
-• Crean trabajos de arte basados en temas contingentes o de interés personal.
-• Crean dibujos, pinturas y murales, usando diferentes materiales, herramientas y procedimientos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>4° Básico</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C38" s="3" t="inlineStr">
-        <is>
-          <t>Expresar y crear visualmente</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>OA 2</t>
-        </is>
-      </c>
-      <c r="E38" s="3" t="inlineStr">
-        <is>
-          <t>Aplicar elementos del lenguaje visual (incluidos los de niveles anteriores) en sus trabajos de arte, con diversos propósitos expresivos y creativos: › líneas de contorno › color (tono y matiz) › forma (figurativa y no figurativa)</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Aplicar</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="inlineStr">
-        <is>
-          <t>• Identifican y describen formas figurativas y no figurativas en obras de arte, pieles de animales e imágenes microscópicas, entre otros.
-• Aplican elementos del lenguaje visual en su trabajo de arte (formas figurativas y no figurativas) con distintos propósitos expresivos y creativos.
-• Identifican y describen líneas de contorno en arte rupestre chileno y objetos de culturas precolombinas.
-• Elaboran pinturas y objetos de artesanía, aplicando conceptos del lenguaje visual, como línea de contorno.
-• Aplican elementos del lenguaje visual (línea de contorno) en su trabajo de arte con distintos propósitos expresivos.
-• Identifican y describen el uso de tonos y matices en la naturaleza y en obras del arte precolombino.
-• Experimentan con colores puros para obtener sus tonos y matices por medio de la pintura.
-• Crean trabajos de arte con distintos propósitos expresivos en forma libre y espontánea, aplicando conceptos del lenguaje visual como tonos y matices.
-• Identifican y describen formas figurativas y no figurativas en obras de arte.
-• Elaboran trabajos de arte, aplicando conceptos del lenguaje visual como forma figurativa y/o no figurativa y otros de los niveles anteriores.</t>
-        </is>
-      </c>
-    </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
         <is>
@@ -2299,82 +2308,30 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>Expresar y crear visualmente</t>
+          <t>Apreciar y responder frente al arte</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>OA 3</t>
+          <t>OA 4</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>Crear trabajos de arte a partir de experiencias, intereses y temas del entorno natural, cultural y artístico, demostrando manejo de: › materiales de modelado, de reciclaje, naturales, papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales › herramientas para dibujar, pintar, cortar, unir, modelar y tecnológicas (pincel, tijera, mirete, computador, cámara fotográfica, entre otras) › procedimientos de dibujo, pintura, grabado, escultura, técnicas mixtas, artesanía, fotografía, entre otros</t>
+          <t>Describir sus observaciones de obras de arte y objetos, usando elementos del lenguaje visual y expresando lo que sienten y piensan. (Observar anualmente al menos 15 obras de arte y artesanía local y chilena, 15 de arte latinoamericano y 15 de arte universal).</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Crear</t>
+          <t>Analizar</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
-        <is>
-          <t>• Experimentan e incorporan posibilidades de expresión con nuevos materiales y recursos de expresión visual.
-• Seleccionan y usan adecuadamente materiales, herramientas y procedimientos técnicos, explicando sus preferencias (por ejemplo: pasteles grasos, plumones, lápices acuarelables, témpera, acuarela, tintas, materiales naturales y de reciclaje, entre otros).
-• Crean esculturas y pinturas con temas relacionados con la naturaleza, el paisaje chileno, fenómenos de la naturaleza y temas personales.
-• Demuestran manejo de procedimientos de pintura y escultura (pintura con lápices o pinturas al agua, mosaico, escultura con materiales naturales, entre otros).
-• Crean pinturas y objetos de artesanía basados en la observación del arte precolombino e ideas personales.
-• Seleccionan adecuadamente materiales herramientas y procedimientos técnicos en relación con el propósito expresivo.
-• Explican preferencias por determinados materiales, herramientas y procedimientos.
-• Demuestran manejo de materiales como papeles, cartones, pinturas, material de reciclaje y natural, entre otros, y de herramientas como tijeras, pinceles, lápices, plumones, estecas, entre otras.
-• Demuestran manejo de procedimientos de pintura y artesanía (pintura con témpera, acrílico, técnicas mixtas y cerámica).
-• Experimentan e incorporan posibilidades de expresión con nuevos materiales y procedimientos en sus pinturas y objetos artesanales.
-• Seleccionan adecuadamente materiales, herramientas y procedimientos técnicos en relación con trabajos de arte u objeto de artesanía.
-• Explican preferencias por determinados materiales, herramientas y procedimientos creativos.
-• Crean esculturas y pinturas por medio de su imaginación y la observacion de diferentes obras y objetos de las culturas precolombinas.
-• Demuestran manejo de procedimientos de dibujo, pintura y escultura.
-• Demuestran manejo de materiales como papeles, cartones, pinturas, tintas y acuarelas, entre otros, y herramientas como tijeras, pinceles, lápices y plumones, entre otras.
-• Experimentan e incorporan nuevas posibilidades de expresión con distintos materiales y recursos de expresión visuales.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>4° Básico</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C40" s="3" t="inlineStr">
-        <is>
-          <t>Apreciar y responder frente al arte</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>OA 4</t>
-        </is>
-      </c>
-      <c r="E40" s="3" t="inlineStr">
-        <is>
-          <t>Describir sus observaciones de obras de arte y objetos, usando elementos del lenguaje visual y expresando lo que sienten y piensan. (Observar anualmente al menos 15 obras de arte y artesanía local y chilena, 15 de arte latinoamericano y 15 de arte universal).</t>
-        </is>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>Analizar</t>
-        </is>
-      </c>
-      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>• Describen imágenes, videos y obras de arte sobre la naturaleza y el paisaje americano, usando elementos del lenguaje visual (línea, forma y color).
 • Reconocen y describen procedimientos de pintura, escultura y artesanía en obras de arte y objetos de artesanía.
@@ -2394,38 +2351,38 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>4° Básico</t>
         </is>
       </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C41" s="5" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C40" s="3" t="inlineStr">
         <is>
           <t>Apreciar y responder frente al arte</t>
         </is>
       </c>
-      <c r="D41" s="4" t="inlineStr">
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>OA 5</t>
         </is>
       </c>
-      <c r="E41" s="5" t="inlineStr">
+      <c r="E40" s="3" t="inlineStr">
         <is>
           <t>Describir fortalezas y aspectos a mejorar en el trabajo de arte personal y de sus pares, aplicando criterios de uso de materiales, procedimientos técnicos y propósito expresivo.</t>
         </is>
       </c>
-      <c r="F41" s="4" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Evaluar</t>
         </is>
       </c>
-      <c r="G41" s="5" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>• Exponen y hablan de sus trabajos de arte y artesanía.
 • Describen los trabajos personales y de sus pares, resaltando fortalezas y aspectos a mejorar con respecto al uso de los materiales, procedimientos y aplicación de elementos de lenguaje visual.
@@ -2439,6 +2396,51 @@
         </is>
       </c>
     </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>4° Básico</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Apreciar y responder frente al arte</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>OA 5</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>Describir fortalezas y aspectos a mejorar en el trabajo de arte personal y de sus pares, aplicando criterios de uso de materiales, procedimientos técnicos y propósito expresivo.</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Analizar</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>• Exponen y hablan de sus trabajos de arte y artesanía.
+• Describen los trabajos personales y de sus pares, resaltando fortalezas y aspectos a mejorar con respecto al uso de los materiales, procedimientos y aplicación de elementos de lenguaje visual.
+• Describen posibles significados, temas y emociones que transmiten sus trabajos personales y los de sus pares.
+• Comparan trabajos de arte, usando criterios relacionados con la aplicación de lenguaje visual.
+• Usan adecuadamente el vocabulario y términos de lenguaje visual (tipos de líneas, color, forma y textura).
+• Exponen y hablan de sus trabajos de arte y describen sus características y propósitos expresivos.
+• Describen y relacionan lo que han tratado de expresar y los resultados obtenidos en sus trabajos de arte (por ejemplo: usé colores cálidos para que la escena pareciera más alegre, usé líneas gruesas para darle más importancia al rostro).
+• Analizan y describen los trabajos personales y de sus pares, usando el vocabulario adecuado y resaltando fortalezas y aspectos e ideas a mejorar con respecto al uso de materiales, procedimientos técnicos y propósitos expresivos, de manera respetuosa.
+• Comparan trabajos de arte y los seleccionan, usando criterios relacionados con la aplicación de lenguaje visual y el propósito expresivo.</t>
+        </is>
+      </c>
+    </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
@@ -2462,15 +2464,67 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
+          <t>Crear trabajos de arte y diseños a partir de sus propias ideas y de la observación del: › entorno cultural: Chile, su paisaje y sus costumbres en el pasado y en el presente › entorno artístico: impresionismo y postimpresionismo; y diseño en Chile, Latinoamérica y del resto del mundo</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t>• Registran sus propias ideas y aquellas de las observaciones del entorno cultural, usando diversos métodos para sus trabajos de arte (por ejemplo: toman fotografías, recolectan imágenes, realizan bocetos, escriben, otros).
+• Pintan creativamente, usando diferentes procedimientos, basados en la observación de obras de arte de la corriente impresionista y postimpresionista.
+• Realizan esculturas creativas, usando diferentes procedimientos, basados en la observación de obras de arte.
+• Observan y describen temas, procedimientos, materiales y diversos medios expresivos usados en el arte chileno.
+• Seleccionan materiales y procedimientos para la creación individual (pintura, escultura y representaciones, entre otros).
+• Crean pinturas originales basadas en paisajes y costumbres chilenas (flora, fauna, relieve y fiestas nacionales, entre otras), aplicando los procedimientos de manera adecuada.
+• Crean esculturas y relieves basados en costumbres y arquitectura chilena, usando materiales y procedimientos adecuadamente.
+• Describen objetos de diseño de diferentes épocas y culturas en relación con el objetivo para el que fueron diseñados y el uso de elementos de lenguaje visual, como forma, color y texturas.
+• Proponen modificaciones o innovaciones a objetos de uso cotidiano a partir del análisis y observación de estos.
+• Diseñan objetos sencillos, respondiendo a distintos desafíos que se les presentan.
+• Diseñan y construyen objetos útiles a partir de elementos de la naturaleza.
+• Realizan diseños gráficos a partir de la observación de afiches, etiquetas y otros elementos.
+• Desarrollan proyectos de diseño basados en diferentes desafíos, considerando la etapa inicial del desarrollo de las ideas por medio de diversos métodos (por ejemplo: toman fotografías, recolectan imágenes de diarios y revistas, realizan bocetos, entre, otros).
+• Usan una variedad de métodos para desarrollar ideas para sus diseños y responder a desafíos.
+• Crean, aplicando las etapas del proceso creativo: - vestuario y accesorios (sombreros), teniendo como referente a las culturas indígenas americanas - máscaras a partir de su imaginación - textiles según sus propios intereses.
+• Desarrollan proyectos de diseño teatral o de celebraciones escolares basados en diferentes desafíos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>5° Básico</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Expresar y crear visualmente</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>OA 1</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
           <t>Crear trabajos de arte y diseños a partir de sus propias ideas y de la observación del: entorno cultural: Chile, su paisaje y sus costumbres en el pasado y en el presente; entorno artístico: impresionismo y postimpresionismo; y diseño en Chile, Latinoamérica y del resto del mundo</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F43" s="4" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G42" s="3" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
         <is>
           <t>• Registran sus propias ideas y aquellas de las observaciones del entorno cultural, usando diversos métodos para sus trabajos de arte (por ejemplo: toman fotografías, recolectan imágenes, realizan bocetos, escriben, otros).
 • Pintan creativamente, usando diferentes procedimientos, basados en la observación de obras de arte de la corriente impresionista y postimpresionista.
@@ -2491,38 +2545,38 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>5° Básico</t>
         </is>
       </c>
-      <c r="B43" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C43" s="5" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C44" s="3" t="inlineStr">
         <is>
           <t>Expresar y crear visualmente</t>
         </is>
       </c>
-      <c r="D43" s="4" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>OA 2</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr">
-        <is>
-          <t>Aplicar y combinar elementos del lenguaje visual (incluidos los de niveles anteriores) en trabajos de arte y diseño con diferentes propósitos expresivos y creativos: color (complementario); formas (abiertas y cerradas); luz y sombra</t>
-        </is>
-      </c>
-      <c r="F43" s="4" t="inlineStr">
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t>Aplicar y combinar elementos del lenguaje visual (incluidos los de niveles anteriores) en trabajos de arte y diseños con diferentes propósitos expresivos y creativos: › color (complementario) › formas (abiertas y cerradas) › luz y sombra</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Aplicar</t>
         </is>
       </c>
-      <c r="G43" s="5" t="inlineStr">
+      <c r="G44" s="3" t="inlineStr">
         <is>
           <t>• Reconocen formas abiertas y cerradas y colores complementarios en obras de arte del impresionismo y postimpresionismo.
 • Pintan aplicando los colores complementarios con fines expresivos y creativos.
@@ -2533,62 +2587,6 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>5° Básico</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C44" s="3" t="inlineStr">
-        <is>
-          <t>Expresar y crear visualmente</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>OA 3</t>
-        </is>
-      </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t>Crear trabajos de arte y diseños a partir de diferentes desafíos y temas del entorno cultural y artístico, demostrando dominio en el uso de: materiales de modelado, de reciclaje, naturales papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales; herramientas para dibujar, pintar, cortar unir, modelar y tecnológicas (brocha, sierra de calar, esteca, cámara de video y proyector multimedia, entre otros); procedimientos de pintura, escultura, construcción, fotografía, video, diseño gráfico digital, entre otros</t>
-        </is>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t>• Aplican los diferentes procedimientos técnicos en forma innovadora.
-• Buscan soluciones frente a dificultades al aplicar los diferentes procedimientos técnicos.
-• Crean pinturas y esculturas, utilizando diversos procedimientos de pintura en sus trabajos de arte, basados en la observación de pinturas impresionistas y postimpresionistas.
-• Explican el uso de luces y sombras por medio de fotografías.
-• Demuestran dominio en el manejo de materiales (por ejemplo: témpera, tintas, acrílico, anilina, greda, papel maché, entre otros), herramientas y procedimientos de pintura y escultura (pintura con diversas pinceladas, modelado en greda o papel maché, tallado en yeso, entre otros).
-• Crean pinturas, relieves y esculturas basados en la observación de la pintura, escultura y costumbres de Chile.
-• Crean dípticos o trípticos, aplicando técnicas de pintura.
-• Buscan soluciones frente a dificultades al aplicar los diferentes procedimientos técnicos, demostrando dominio de los materiales y herramientas para realizar pinturas y esculturas (por ejemplo: témpera, tintas, acrílico, cartones, greda, arcilla, papel maché, entre otros).
-• Innovan al aplicar los diferentes procedimientos técnicos.
-• Se evidencia un buen manejo de algunos procedimientos de pintura y escultura.
-• Desarrollan ideas por medio de herramientas computacionales para el diseño gráfico.
-• Proponen soluciones creativas a desafíos en torno al diseño y aplican algunas etapas del proceso creativo, como generar ideas, explorar, revisar, presentar y evaluar.
-• Justifican adecuadamente la selección de materiales, herramientas y procedimientos técnicos y/o tecnológicos en relación con los propósitos creativos de sus proyectos de diseño.
-• Realizan diseños de objetos, considerando las características de los diversos materiales.
-• Investigan acerca de procedimientos técnicos y materiales utilizados en el diseño teatral, de vestuario, máscaras y objetos del pasado y el presente.
-• Realizan diseños para objetos de diversa índole (títeres, escenografías, ambientaciones, otros), considerando las características de los diversos materiales y los requerimientos del proyecto.
-• Utilizan algunas herramientas computacionales, máquinas fotográficas y video para el diseño.
-• Seleccionan adecuadamente materiales herramientas y procedimientos técnicos y/o tecnológicos en relación con los propósitos creativos de sus proyectos de diseño.
-• Dominan e innovan al usar materiales, herramientas y procedimientos seleccionados.
-• Buscan soluciones frente a dificultades al aplicar diferentes procedimientos técnicos para la elaboración de objetos.</t>
-        </is>
-      </c>
-    </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
@@ -2602,167 +2600,25 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>Apreciar y responder frente al arte</t>
+          <t>Expresar y crear visualmente</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>OA 4</t>
+          <t>OA 2</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>Analizar e interpretar obras de arte y diseño en relación con la aplicación del lenguaje visual, contextos, materiales, estilos u otros.</t>
+          <t>Aplicar y combinar elementos del lenguaje visual (incluidos los de niveles anteriores) en trabajos de arte y diseño con diferentes propósitos expresivos y creativos: color (complementario); formas (abiertas y cerradas); luz y sombra</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Analizar</t>
+          <t>Aplicar</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>• Buscan y seleccionan información relevante sobre los elementos del contexto (históricos y sociales) y los artistas y obras de arte del impresionismo y postimpresionismo y la presentan usando diferentes medios (informes, powerpoint, entrevistas virtuales, otros).
-• Observan y analizan obras artísticas de los estilos impresionista y postimpresionista en relación con características visuales, temas, materiales y expresividad.
-• Observan e interpretan obras de arte de los estilos impresionista y postimpresionista (su color, volumen, expresión, significado, etc.) y explican sus apreciaciones personales.
-• Exponen trabajos basados en la búsqueda de información usando TIC y otros medios.
-• Describen posibles usos, funciones, significados y aplicación del lenguaje visual en objetos de diseño.
-• Investigan acerca de un objeto, estableciendo relaciones entre elementos de su contexto, materiales y cómo estos se reflejan en el diseño.
-• Analizan objetos de diseños de diversas épocas y contextos en relación con los objetivos para los que fueron diseñados, características visuales, materiales y medios.
-• Interpretan objetos y elementos de diferentes tipos de diseño en relación con su significado y contexto.
-• Presentan sus investigaciones, usando TIC y otros medios.
-• Investigan acerca de la evolución de un elemento de diseño, estableciendo relaciones entre elementos de su contexto, materiales, elementos de lenguaje visual y cómo ellos se reflejan en el diseño.
-• Analizan diseños de vestuario y teatrales provenientes de diferentes épocas, culturas y estilos en relación con características visuales, contextos y materiales.
-• Explican apreciaciones personales acerca de diferentes objetos de diseño.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>5° Básico</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>Apreciar y responder frente al arte</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>OA 5</t>
-        </is>
-      </c>
-      <c r="E46" s="3" t="inlineStr">
-        <is>
-          <t>Describir y comparar trabajos de arte y diseño personales y de sus pares, considerando: fortalezas y aspectos a mejorar; uso de materiales y procedimientos; aplicación de elementos de lenguaje visual; propósitos expresivos</t>
-        </is>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>Analizar</t>
-        </is>
-      </c>
-      <c r="G46" s="3" t="inlineStr">
-        <is>
-          <t>• Comparan trabajos de arte y obras de arte de los estilos impresionista y postimpresionista en relación con características visuales, temas, materiales, uso de procedimientos, aplicación de elementos del lenguaje visual y expresividad.
-• Describen las fortalezas y aspectos a mejorar en los trabajos personales y de sus pares en relación con la selección de temas, ideas, manejo de los materiales y procedimientos, la aplicación de elementos del lenguaje visual y el propósito expresivo.
-• Justifican las apreciaciones personales acerca de trabajos personales y de sus compañeros, utilizando el vocabulario aprendido en forma adecuada (tipos de líneas, color, forma y textura).
-• Justifican el proyecto de diseño propio y de sus compañeros y proponen ideas para mejorarlo usando criterios como: propósito del proyecto, funcionalidad del elemento u objeto, estética del diseño (color, forma, textura), aplicación de elementos de lenguaje visual (color, forma, textura, otros), uso adecuado de materiales y herramientas, originalidad de la propuesta.
-• Comparan objetos de diseño, usando como criterios: uso de materiales y procedimientos, aplicación de elementos de lenguaje visual, propósitos expresivos.
-• Seleccionan trabajos de arte, justificando sus preferencias, para ser expuestos en el establecimiento o en la página web.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>5° Básico</t>
-        </is>
-      </c>
-      <c r="B47" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>Expresar y crear visualmente</t>
-        </is>
-      </c>
-      <c r="D47" s="4" t="inlineStr">
-        <is>
-          <t>OA 1</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>Crear trabajos de arte y diseños a partir de sus propias ideas y de la observación del: › entorno cultural: Chile, su paisaje y sus costumbres en el pasado y en el presente › entorno artístico: impresionismo y postimpresionismo; y diseño en Chile, Latinoamérica y del resto del mundo</t>
-        </is>
-      </c>
-      <c r="F47" s="4" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>• Registran sus propias ideas y aquellas de las observaciones del entorno cultural, usando diversos métodos para sus trabajos de arte (por ejemplo: toman fotografías, recolectan imágenes, realizan bocetos, escriben, otros).
-• Pintan creativamente, usando diferentes procedimientos, basados en la observación de obras de arte de la corriente impresionista y postimpresionista.
-• Realizan esculturas creativas, usando diferentes procedimientos, basados en la observación de obras de arte.
-• Observan y describen temas, procedimientos, materiales y diversos medios expresivos usados en el arte chileno.
-• Seleccionan materiales y procedimientos para la creación individual (pintura, escultura y representaciones, entre otros).
-• Crean pinturas originales basadas en paisajes y costumbres chilenas (flora, fauna, relieve y fiestas nacionales, entre otras), aplicando los procedimientos de manera adecuada.
-• Crean esculturas y relieves basados en costumbres y arquitectura chilena, usando materiales y procedimientos adecuadamente.
-• Describen objetos de diseño de diferentes épocas y culturas en relación con el objetivo para el que fueron diseñados y el uso de elementos de lenguaje visual, como forma, color y texturas.
-• Proponen modificaciones o innovaciones a objetos de uso cotidiano a partir del análisis y observación de estos.
-• Diseñan objetos sencillos, respondiendo a distintos desafíos que se les presentan.
-• Diseñan y construyen objetos útiles a partir de elementos de la naturaleza.
-• Realizan diseños gráficos a partir de la observación de afiches, etiquetas y otros elementos.
-• Desarrollan proyectos de diseño basados en diferentes desafíos, considerando la etapa inicial del desarrollo de las ideas por medio de diversos métodos (por ejemplo: toman fotografías, recolectan imágenes de diarios y revistas, realizan bocetos, entre, otros).
-• Usan una variedad de métodos para desarrollar ideas para sus diseños y responder a desafíos.
-• Crean, aplicando las etapas del proceso creativo: - vestuario y accesorios (sombreros), teniendo como referente a las culturas indígenas americanas - máscaras a partir de su imaginación - textiles según sus propios intereses.
-• Desarrollan proyectos de diseño teatral o de celebraciones escolares basados en diferentes desafíos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>5° Básico</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>Expresar y crear visualmente</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
-        <is>
-          <t>OA 2</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="inlineStr">
-        <is>
-          <t>Aplicar y combinar elementos del lenguaje visual (incluidos los de niveles anteriores) en trabajos de arte y diseños con diferentes propósitos expresivos y creativos: › color (complementario) › formas (abiertas y cerradas) › luz y sombra</t>
-        </is>
-      </c>
-      <c r="F48" s="2" t="inlineStr">
-        <is>
-          <t>Aplicar</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>• Reconocen formas abiertas y cerradas y colores complementarios en obras de arte del impresionismo y postimpresionismo.
 • Pintan aplicando los colores complementarios con fines expresivos y creativos.
@@ -2773,38 +2629,38 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>5° Básico</t>
         </is>
       </c>
-      <c r="B49" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C49" s="5" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C46" s="3" t="inlineStr">
         <is>
           <t>Expresar y crear visualmente</t>
         </is>
       </c>
-      <c r="D49" s="4" t="inlineStr">
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>OA 3</t>
         </is>
       </c>
-      <c r="E49" s="5" t="inlineStr">
+      <c r="E46" s="3" t="inlineStr">
         <is>
           <t>Crear trabajos de arte y diseños a partir de diferentes desafíos y temas del entorno cultural y artístico, demostrando dominio en el uso de: › materiales de modelado, de reciclaje, naturales papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales › herramientas para dibujar, pintar, cortar unir, modelar y tecnológicas (brocha, sierra de calar, esteca, cámara de video y proyector multimedia, entre otros) › procedimientos de pintura, escultura, construcción, fotografía, video, diseño gráfico digital, entre otros</t>
         </is>
       </c>
-      <c r="F49" s="4" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G49" s="5" t="inlineStr">
+      <c r="G46" s="3" t="inlineStr">
         <is>
           <t>• Aplican los diferentes procedimientos técnicos en forma innovadora.
 • Buscan soluciones frente a dificultades al aplicar los diferentes procedimientos técnicos.
@@ -2830,38 +2686,94 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>5° Básico</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C50" s="3" t="inlineStr">
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Expresar y crear visualmente</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>OA 3</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>Crear trabajos de arte y diseños a partir de diferentes desafíos y temas del entorno cultural y artístico, demostrando dominio en el uso de: materiales de modelado, de reciclaje, naturales papeles, cartones, pegamentos, lápices, pinturas, textiles e imágenes digitales; herramientas para dibujar, pintar, cortar unir, modelar y tecnológicas (brocha, sierra de calar, esteca, cámara de video y proyector multimedia, entre otros); procedimientos de pintura, escultura, construcción, fotografía, video, diseño gráfico digital, entre otros</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>• Aplican los diferentes procedimientos técnicos en forma innovadora.
+• Buscan soluciones frente a dificultades al aplicar los diferentes procedimientos técnicos.
+• Crean pinturas y esculturas, utilizando diversos procedimientos de pintura en sus trabajos de arte, basados en la observación de pinturas impresionistas y postimpresionistas.
+• Explican el uso de luces y sombras por medio de fotografías.
+• Demuestran dominio en el manejo de materiales (por ejemplo: témpera, tintas, acrílico, anilina, greda, papel maché, entre otros), herramientas y procedimientos de pintura y escultura (pintura con diversas pinceladas, modelado en greda o papel maché, tallado en yeso, entre otros).
+• Crean pinturas, relieves y esculturas basados en la observación de la pintura, escultura y costumbres de Chile.
+• Crean dípticos o trípticos, aplicando técnicas de pintura.
+• Buscan soluciones frente a dificultades al aplicar los diferentes procedimientos técnicos, demostrando dominio de los materiales y herramientas para realizar pinturas y esculturas (por ejemplo: témpera, tintas, acrílico, cartones, greda, arcilla, papel maché, entre otros).
+• Innovan al aplicar los diferentes procedimientos técnicos.
+• Se evidencia un buen manejo de algunos procedimientos de pintura y escultura.
+• Desarrollan ideas por medio de herramientas computacionales para el diseño gráfico.
+• Proponen soluciones creativas a desafíos en torno al diseño y aplican algunas etapas del proceso creativo, como generar ideas, explorar, revisar, presentar y evaluar.
+• Justifican adecuadamente la selección de materiales, herramientas y procedimientos técnicos y/o tecnológicos en relación con los propósitos creativos de sus proyectos de diseño.
+• Realizan diseños de objetos, considerando las características de los diversos materiales.
+• Investigan acerca de procedimientos técnicos y materiales utilizados en el diseño teatral, de vestuario, máscaras y objetos del pasado y el presente.
+• Realizan diseños para objetos de diversa índole (títeres, escenografías, ambientaciones, otros), considerando las características de los diversos materiales y los requerimientos del proyecto.
+• Utilizan algunas herramientas computacionales, máquinas fotográficas y video para el diseño.
+• Seleccionan adecuadamente materiales herramientas y procedimientos técnicos y/o tecnológicos en relación con los propósitos creativos de sus proyectos de diseño.
+• Dominan e innovan al usar materiales, herramientas y procedimientos seleccionados.
+• Buscan soluciones frente a dificultades al aplicar diferentes procedimientos técnicos para la elaboración de objetos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>5° Básico</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>Apreciar y responder frente al arte</t>
         </is>
       </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>OA 4</t>
         </is>
       </c>
-      <c r="E50" s="3" t="inlineStr">
+      <c r="E48" s="3" t="inlineStr">
         <is>
           <t>Analizar e interpretar obras de arte y diseño en relación con la aplicación del lenguaje visual, contextos, materiales, estilos u otros. (Observar anualmente al menos 50 obras de arte y diseño chileno, latinoamericano y universal).</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Analizar</t>
         </is>
       </c>
-      <c r="G50" s="3" t="inlineStr">
+      <c r="G48" s="3" t="inlineStr">
         <is>
           <t>• Buscan y seleccionan información relevante sobre los elementos del contexto (históricos y sociales) y los artistas y obras de arte del impresionismo y postimpresionismo y la presentan usando diferentes medios (informes, powerpoint, entrevistas virtuales, otros).
 • Observan y analizan obras artísticas de los estilos impresionista y postimpresionista en relación con características visuales, temas, materiales y expresividad.
@@ -2879,38 +2791,86 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>5° Básico</t>
         </is>
       </c>
-      <c r="B51" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C51" s="5" t="inlineStr">
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
         <is>
           <t>Apreciar y responder frente al arte</t>
         </is>
       </c>
-      <c r="D51" s="4" t="inlineStr">
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>OA 4</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>Analizar e interpretar obras de arte y diseño en relación con la aplicación del lenguaje visual, contextos, materiales, estilos u otros.</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Analizar</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>• Buscan y seleccionan información relevante sobre los elementos del contexto (históricos y sociales) y los artistas y obras de arte del impresionismo y postimpresionismo y la presentan usando diferentes medios (informes, powerpoint, entrevistas virtuales, otros).
+• Observan y analizan obras artísticas de los estilos impresionista y postimpresionista en relación con características visuales, temas, materiales y expresividad.
+• Observan e interpretan obras de arte de los estilos impresionista y postimpresionista (su color, volumen, expresión, significado, etc.) y explican sus apreciaciones personales.
+• Exponen trabajos basados en la búsqueda de información usando TIC y otros medios.
+• Describen posibles usos, funciones, significados y aplicación del lenguaje visual en objetos de diseño.
+• Investigan acerca de un objeto, estableciendo relaciones entre elementos de su contexto, materiales y cómo estos se reflejan en el diseño.
+• Analizan objetos de diseños de diversas épocas y contextos en relación con los objetivos para los que fueron diseñados, características visuales, materiales y medios.
+• Interpretan objetos y elementos de diferentes tipos de diseño en relación con su significado y contexto.
+• Presentan sus investigaciones, usando TIC y otros medios.
+• Investigan acerca de la evolución de un elemento de diseño, estableciendo relaciones entre elementos de su contexto, materiales, elementos de lenguaje visual y cómo ellos se reflejan en el diseño.
+• Analizan diseños de vestuario y teatrales provenientes de diferentes épocas, culturas y estilos en relación con características visuales, contextos y materiales.
+• Explican apreciaciones personales acerca de diferentes objetos de diseño.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>5° Básico</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>Apreciar y responder frente al arte</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>OA 5</t>
         </is>
       </c>
-      <c r="E51" s="5" t="inlineStr">
+      <c r="E50" s="3" t="inlineStr">
         <is>
           <t>Describir y comparar trabajos de arte y diseño personales y de sus pares, considerando: › fortalezas y aspectos a mejorar › uso de materiales y procedimientos › aplicación de elementos del lenguaje visual › propósitos expresivos</t>
         </is>
       </c>
-      <c r="F51" s="4" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Analizar</t>
         </is>
       </c>
-      <c r="G51" s="5" t="inlineStr">
+      <c r="G50" s="3" t="inlineStr">
         <is>
           <t>• Comparan trabajos de arte y obras de arte de los estilos impresionista y postimpresionista en relación con características visuales, temas, materiales, uso de procedimientos, aplicación de elementos del lenguaje visual y expresividad.
 • Describen las fortalezas y aspectos a mejorar en los trabajos personales y de sus pares en relación con la selección de temas, ideas, manejo de los materiales y procedimientos, la aplicación de elementos del lenguaje visual y el propósito expresivo.
@@ -2922,6 +2882,48 @@
         </is>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>5° Básico</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>Apreciar y responder frente al arte</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>OA 5</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>Describir y comparar trabajos de arte y diseño personales y de sus pares, considerando: fortalezas y aspectos a mejorar; uso de materiales y procedimientos; aplicación de elementos de lenguaje visual; propósitos expresivos</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Analizar</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>• Comparan trabajos de arte y obras de arte de los estilos impresionista y postimpresionista en relación con características visuales, temas, materiales, uso de procedimientos, aplicación de elementos del lenguaje visual y expresividad.
+• Describen las fortalezas y aspectos a mejorar en los trabajos personales y de sus pares en relación con la selección de temas, ideas, manejo de los materiales y procedimientos, la aplicación de elementos del lenguaje visual y el propósito expresivo.
+• Justifican las apreciaciones personales acerca de trabajos personales y de sus compañeros, utilizando el vocabulario aprendido en forma adecuada (tipos de líneas, color, forma y textura).
+• Justifican el proyecto de diseño propio y de sus compañeros y proponen ideas para mejorarlo usando criterios como: propósito del proyecto, funcionalidad del elemento u objeto, estética del diseño (color, forma, textura), aplicación de elementos de lenguaje visual (color, forma, textura, otros), uso adecuado de materiales y herramientas, originalidad de la propuesta.
+• Comparan objetos de diseño, usando como criterios: uso de materiales y procedimientos, aplicación de elementos de lenguaje visual, propósitos expresivos.
+• Seleccionan trabajos de arte, justificando sus preferencias, para ser expuestos en el establecimiento o en la página web.</t>
+        </is>
+      </c>
+    </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
@@ -2930,7 +2932,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
@@ -2979,7 +2981,7 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -3023,7 +3025,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C54" s="3" t="inlineStr">
@@ -3071,7 +3073,7 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C55" s="5" t="inlineStr">
@@ -3127,7 +3129,7 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -3178,7 +3180,7 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
@@ -3221,7 +3223,7 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
@@ -3265,7 +3267,7 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
@@ -3311,7 +3313,7 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
@@ -3359,7 +3361,7 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
@@ -3401,7 +3403,7 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
@@ -3468,6 +3470,56 @@
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>• Describen percepciones, sentimientos e ideas que les genera la observación de manifestaciones visuales con temas de persona y medioambiente.
+• Seleccionan manifestaciones visuales o temas como referentes para el desarrollo de sus trabajos visuales.
+• Crean textos acerca de historias urbanas.
+• Seleccionan medios visuales expresivos para desarrollar trabajos y proyectos visuales.
+• Seleccionan materiales, herramientas y procedimientos de acuerdo al tipo de trabajo visual y el propósito expresivo.
+• Proponen diferentes maneras de trabajar con materiales, herramientas y procedimientos.
+• Desarrollan ideas originales para trabajos visuales por medio de bocetos, maquetas, fotografías y TIC.
+• Seleccionan ideas para el desarrollo de proyectos y trabajos visuales.
+• Crean trabajos y proyectos visuales considerando ideas y la selección de materialidades.
+• Se evidencia en sus trabajos o proyectos visuales la expresión de propósitos, sentimientos e ideas personales.
+• Se evidencia en sus trabajos visuales la narración de historias.
+• Se evidencia en sus trabajos o proyectos la relación entre materialidad, lenguaje visual y propósitos expresivos.
+• Desarrollan ideas para diseños que consideran la relación con la naturaleza y el medio ambiente, por medio de la elaboración de bocetos y textos.
+• Expresan propósitos expresivos, sentimientos e ideas personales en sus trabajos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>8° Básico</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C64" s="3" t="inlineStr">
+        <is>
+          <t>Expresar y crear visualmente</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>OA 1</t>
+        </is>
+      </c>
+      <c r="E64" s="3" t="inlineStr">
+        <is>
+          <t>Crear trabajos visuales basados en la apreciación y el análisis de manifestaciones estéticas referidas a la relación entre personas, naturaleza y medioambiente, en diferentes contextos.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G64" s="3" t="inlineStr">
         <is>
           <t>• Describen percepciones, sentimientos e ideas que les genera la observación de manifestaciones visuales con temas de persona y naturaleza.
 • Seleccionan manifestaciones visuales o temas como referentes para el desarrollo de sus trabajos visuales.
@@ -3484,38 +3536,85 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>8° Básico</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C65" s="5" t="inlineStr">
         <is>
           <t>Expresar y crear visualmente</t>
         </is>
       </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>OA 2</t>
         </is>
       </c>
-      <c r="E64" s="3" t="inlineStr">
+      <c r="E65" s="5" t="inlineStr">
         <is>
           <t>Crear trabajos visuales a partir de diferentes desafíos creativos, experimentando con materiales sustentables en técnicas de impresión, papeles y textiles.</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F65" s="4" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G64" s="3" t="inlineStr">
+      <c r="G65" s="5" t="inlineStr">
+        <is>
+          <t>• Describen percepciones, sentimientos e ideas que les genera la observación de grabados.
+• Proponen temas de su interés para desarrollar trabajos visuales.
+• Experimentan con materiales, herramientas y procedimientos de grabado.
+• Experimentan con diferentes colores y soportes para imprimir sus grabados.
+• Desarrollan ideas originales por medio de bocetos para sus grabados.
+• Usan los resultados de sus experimentaciones en sus trabajos de arte.
+• Describen percepciones, sentimientos e ideas que les genera la observación de textiles y arte textil.
+• Proponen temas de su interés para desarrollar textiles y arte textil.
+• Experimentan con materiales, herramientas y procedimientos de textilería y arte textil.
+• Experimentan con diferentes materiales reciclables para elaborar textiles y trabajos de arte textil.
+• Usan los resultados de sus experimentaciones textiles y trabajos de arte textil.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>8° Básico</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>Expresar y crear visualmente</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>OA 2</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="inlineStr">
+        <is>
+          <t>Crear trabajos visuales a partir de diferentes desafíos creativos, experimentando con materiales sustentables en técnicas de impresión, papeles y textiles.</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
         <is>
           <t>• Describen percepciones, sentimientos e ideas que les genera la observación de grabados.
 • Proponen temas de su interés para desarrollar trabajos visuales.
@@ -3532,38 +3631,38 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>8° Básico</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C65" s="5" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
         <is>
           <t>Expresar y crear visualmente</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>OA 3</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr">
+      <c r="E67" s="5" t="inlineStr">
         <is>
           <t>Crear trabajos visuales a partir de diferentes desafíos creativos, usando medios de expresión contemporáneos como la instalación.</t>
         </is>
       </c>
-      <c r="F65" s="4" t="inlineStr">
+      <c r="F67" s="4" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G65" s="5" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>• Describen percepciones, sentimientos e ideas que les genera la observación de diferentes instalaciones.
 • Seleccionan temas y/o conceptos para el desarrollo de una instalación.
@@ -3576,38 +3675,138 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>8° Básico</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>Expresar y crear visualmente</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>OA 3</t>
+        </is>
+      </c>
+      <c r="E68" s="3" t="inlineStr">
+        <is>
+          <t>Crear trabajos visuales a partir de diferentes desafíos creativos, usando medios de expresión contemporáneos como la instalación.</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G68" s="3" t="inlineStr">
+        <is>
+          <t>• Describen percepciones, sentimientos e ideas que les genera la observación de diferentes instalaciones.
+• Seleccionan temas y/o conceptos para el desarrollo de una instalación.
+• Desarrollan ideas originales para la creación una instalación por medio de bocetos, representaciones tridimensionales, fotografías, textos y TIC.
+• Seleccionan medios expresivos, materialidades y elementos del lenguaje visual considerando el propósito expresivo de su instalación.
+• Analizan los procedimientos necesarios para crear su instalación considerando la distribución espacial, recorridos e interacción con el espectador.
+• Crean una instalación basados en diversos temas, ideas e intereses personales.
+• Se evidencia en sus instalaciones la expresión de propósitos, sentimientos e ideas personales.
+• Se evidencia en sus instalaciones el uso de medios expresivos, materialidad, lenguaje visual y propósitos expresivos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>8° Básico</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>Apreciar y responder frente al arte</t>
         </is>
       </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>OA 4</t>
         </is>
       </c>
-      <c r="E66" s="3" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>Analizar manifestaciones visuales patrimoniales y contemporáneas, contemplando criterios como: contexto, materialidad, lenguaje visual y propósito expresivo.</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F69" s="4" t="inlineStr">
         <is>
           <t>Analizar</t>
         </is>
       </c>
-      <c r="G66" s="3" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>• Describen percepciones, sentimientos e ideas que les genera la observación de manifestaciones visuales con temas de persona y medioambiente.
+• Describen características de materialidades, medios expresivos y lenguaje visual de manifestaciones visuales.
+• Interpretan significados de manifestaciones visuales con temas de persona y medioambiente.
+• Analizan relaciones entre manifestaciones visuales y sus contextos.
+• Describen funciones de manifestaciones visuales.
+• Comparan manifestaciones visuales usando criterios estéticos.
+• Determinan criterios estéticos para interpretar manifestaciones visuales.
+• Sintetizan información de sus investigaciones acerca de creadores y creadoras y manifestaciones visuales con temas de persona y naturaleza.
+• Comunican investigaciones y apreciaciones por medio de infografías y folletos.
+• Comunican investigaciones y apreciaciones por medio de infografías y presentaciones digitales.
+• Describen características de instalaciones considerando a la o al artista referente, uso de medios expresivos, materialidad y uso del lenguaje visual.
+• Describen características de la instalación considerando distribución espacial, recorridos e interacción con los espectadores.
+• Analizan relaciones entre temas y/o conceptos de las instalaciones, uso de medios expresivos, materialidad, lenguaje visual y propósito expresivo.
+• Analizan relaciones entre las instalaciones y sus contextos.
+• Interpretan significados de instalaciones considerando contexto, medios expresivos, materialidad, lenguaje visual y propósito expresivo.
+• Sintetizan información de sus investigaciones en torno a las instalaciones en una presentación.
+• Describen percepciones, sentimientos e ideas que les genera la observación de manifestaciones estéticas de diferentes épocas y contextos.
+• Infieren significados y propósitos de distintos diseños considerando aspectos del contexto, materialidad, lenguaje visual y propósito expresivo.
+• Relacionan el uso de lenguaje visual y elementos del diseño con sensaciones, emociones e ideas que este provoca.
+• Reconocen elementos culturales presentes en diseños de diferentes contextos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>8° Básico</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>Apreciar y responder frente al arte</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>OA 4</t>
+        </is>
+      </c>
+      <c r="E70" s="3" t="inlineStr">
+        <is>
+          <t>Analizar manifestaciones visuales patrimoniales y contemporáneas, contemplando criterios como: contexto, materialidad, lenguaje visual y propósito expresivo.</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>Analizar</t>
+        </is>
+      </c>
+      <c r="G70" s="3" t="inlineStr">
         <is>
           <t>• Describen características de materialidades, medios expresivos y lenguaje visual de manifestaciones visuales.
 • Describen funciones de manifestaciones visuales.
@@ -3632,38 +3831,85 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="4" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>8° Básico</t>
         </is>
       </c>
-      <c r="B67" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C67" s="5" t="inlineStr">
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C71" s="5" t="inlineStr">
         <is>
           <t>Apreciar y responder frente al arte</t>
         </is>
       </c>
-      <c r="D67" s="4" t="inlineStr">
+      <c r="D71" s="4" t="inlineStr">
         <is>
           <t>OA 5</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr">
+      <c r="E71" s="5" t="inlineStr">
         <is>
           <t>Evaluar trabajos visuales personales y de sus pares, considerando criterios como: materialidad, lenguaje visual y propósito expresivo.</t>
         </is>
       </c>
-      <c r="F67" s="4" t="inlineStr">
+      <c r="F71" s="4" t="inlineStr">
         <is>
           <t>Evaluar</t>
         </is>
       </c>
-      <c r="G67" s="5" t="inlineStr">
+      <c r="G71" s="5" t="inlineStr">
+        <is>
+          <t>• Explican ideas para sus trabajos visuales.
+• Explican fortalezas y elementos a mejorar en trabajos personales usando criterios de propósito expresivo, materialidad y utilización del lenguaje visual.
+• Explican fortalezas y elementos a mejorar en trabajos de sus pares usando criterios de propósito expresivo, materialidad y utilización del lenguaje visual.
+• Explican propósitos expresivos de trabajos personales.
+• Justifican la selección de materiales, herramientas y procedimientos desde el punto de vista de sus propósitos expresivos.
+• Justifican el uso del lenguaje visual en sus trabajos visuales según sus propósitos expresivos.
+• Coevalúan trabajos visuales usando criterios de propósito expresivo, materialidad y uso del lenguaje visual.
+• Coevalúan ideas para trabajos visuales usando criterios de propósito expresivo, materialidad y uso del lenguaje visual.
+• Identifican elementos originales de experimentaciones con diferentes materiales, herramientas y procedimientos.
+• Coevalúan las instalaciones usando criterios de propósito expresivo, medios expresivos, materialidad y uso del lenguaje visual.
+• Interpretan trabajos visuales e investigaciones de sus pares desde el punto de vista de la materialidad y propósito expresivo-funcional.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>8° Básico</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>Apreciar y responder frente al arte</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>OA 5</t>
+        </is>
+      </c>
+      <c r="E72" s="3" t="inlineStr">
+        <is>
+          <t>Evaluar trabajos visuales personales y de sus pares, considerando criterios como: materialidad, lenguaje visual y propósito expresivo.</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>Evaluar</t>
+        </is>
+      </c>
+      <c r="G72" s="3" t="inlineStr">
         <is>
           <t>• Explican ideas para sus trabajos visuales.
 • Explican fortalezas y elementos a mejorar en trabajos personales usando criterios de propósito expresivo, materialidad y utilización del lenguaje visual.
@@ -3686,38 +3932,38 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>8° Básico</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C68" s="3" t="inlineStr">
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C73" s="5" t="inlineStr">
         <is>
           <t>Difundir y comunicar</t>
         </is>
       </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="D73" s="4" t="inlineStr">
         <is>
           <t>OA 6</t>
         </is>
       </c>
-      <c r="E68" s="3" t="inlineStr">
+      <c r="E73" s="5" t="inlineStr">
         <is>
           <t>Comparar y valorar espacios de difusión de las artes visuales, considerando: medios de expresión presentes, espacio, montaje, público y aporte a la comunidad.</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F73" s="4" t="inlineStr">
         <is>
           <t>Evaluar</t>
         </is>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>• Representan por medio de croquis sus conocimientos, experiencias y concepciones previas acerca de espacios de difusión de manifestaciones visuales.
 • Describen espacios destinados a la difusión de las artes visuales a partir de lo observado directa y/o virtualmente.
@@ -3727,250 +3973,6 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="4" t="inlineStr">
-        <is>
-          <t>8° Básico</t>
-        </is>
-      </c>
-      <c r="B69" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C69" s="5" t="inlineStr">
-        <is>
-          <t>Expresar y crear visualmente</t>
-        </is>
-      </c>
-      <c r="D69" s="4" t="inlineStr">
-        <is>
-          <t>OA 1</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="inlineStr">
-        <is>
-          <t>Crear trabajos visuales basados en la apreciación y el análisis de manifestaciones estéticas referidas a la relación entre personas, naturaleza y medioambiente, en diferentes contextos.</t>
-        </is>
-      </c>
-      <c r="F69" s="4" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G69" s="5" t="inlineStr">
-        <is>
-          <t>• Describen percepciones, sentimientos e ideas que les genera la observación de manifestaciones visuales con temas de persona y medioambiente.
-• Seleccionan manifestaciones visuales o temas como referentes para el desarrollo de sus trabajos visuales.
-• Crean textos acerca de historias urbanas.
-• Seleccionan medios visuales expresivos para desarrollar trabajos y proyectos visuales.
-• Seleccionan materiales, herramientas y procedimientos de acuerdo al tipo de trabajo visual y el propósito expresivo.
-• Proponen diferentes maneras de trabajar con materiales, herramientas y procedimientos.
-• Desarrollan ideas originales para trabajos visuales por medio de bocetos, maquetas, fotografías y TIC.
-• Seleccionan ideas para el desarrollo de proyectos y trabajos visuales.
-• Crean trabajos y proyectos visuales considerando ideas y la selección de materialidades.
-• Se evidencia en sus trabajos o proyectos visuales la expresión de propósitos, sentimientos e ideas personales.
-• Se evidencia en sus trabajos visuales la narración de historias.
-• Se evidencia en sus trabajos o proyectos la relación entre materialidad, lenguaje visual y propósitos expresivos.
-• Desarrollan ideas para diseños que consideran la relación con la naturaleza y el medio ambiente, por medio de la elaboración de bocetos y textos.
-• Expresan propósitos expresivos, sentimientos e ideas personales en sus trabajos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>8° Básico</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C70" s="3" t="inlineStr">
-        <is>
-          <t>Expresar y crear visualmente</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>OA 2</t>
-        </is>
-      </c>
-      <c r="E70" s="3" t="inlineStr">
-        <is>
-          <t>Crear trabajos visuales a partir de diferentes desafíos creativos, experimentando con materiales sustentables en técnicas de impresión, papeles y textiles.</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G70" s="3" t="inlineStr">
-        <is>
-          <t>• Describen percepciones, sentimientos e ideas que les genera la observación de grabados.
-• Proponen temas de su interés para desarrollar trabajos visuales.
-• Experimentan con materiales, herramientas y procedimientos de grabado.
-• Experimentan con diferentes colores y soportes para imprimir sus grabados.
-• Desarrollan ideas originales por medio de bocetos para sus grabados.
-• Usan los resultados de sus experimentaciones en sus trabajos de arte.
-• Describen percepciones, sentimientos e ideas que les genera la observación de textiles y arte textil.
-• Proponen temas de su interés para desarrollar textiles y arte textil.
-• Experimentan con materiales, herramientas y procedimientos de textilería y arte textil.
-• Experimentan con diferentes materiales reciclables para elaborar textiles y trabajos de arte textil.
-• Usan los resultados de sus experimentaciones textiles y trabajos de arte textil.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="4" t="inlineStr">
-        <is>
-          <t>8° Básico</t>
-        </is>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C71" s="5" t="inlineStr">
-        <is>
-          <t>Expresar y crear visualmente</t>
-        </is>
-      </c>
-      <c r="D71" s="4" t="inlineStr">
-        <is>
-          <t>OA 3</t>
-        </is>
-      </c>
-      <c r="E71" s="5" t="inlineStr">
-        <is>
-          <t>Crear trabajos visuales a partir de diferentes desafíos creativos, usando medios de expresión contemporáneos como la instalación.</t>
-        </is>
-      </c>
-      <c r="F71" s="4" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G71" s="5" t="inlineStr">
-        <is>
-          <t>• Describen percepciones, sentimientos e ideas que les genera la observación de diferentes instalaciones.
-• Seleccionan temas y/o conceptos para el desarrollo de una instalación.
-• Desarrollan ideas originales para la creación una instalación por medio de bocetos, representaciones tridimensionales, fotografías, textos y TIC.
-• Seleccionan medios expresivos, materialidades y elementos del lenguaje visual considerando el propósito expresivo de su instalación.
-• Analizan los procedimientos necesarios para crear su instalación considerando la distribución espacial, recorridos e interacción con el espectador.
-• Crean una instalación basados en diversos temas, ideas e intereses personales.
-• Se evidencia en sus instalaciones la expresión de propósitos, sentimientos e ideas personales.
-• Se evidencia en sus instalaciones el uso de medios expresivos, materialidad, lenguaje visual y propósitos expresivos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>8° Básico</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C72" s="3" t="inlineStr">
-        <is>
-          <t>Apreciar y responder frente al arte</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>OA 4</t>
-        </is>
-      </c>
-      <c r="E72" s="3" t="inlineStr">
-        <is>
-          <t>Analizar manifestaciones visuales patrimoniales y contemporáneas, contemplando criterios como: contexto, materialidad, lenguaje visual y propósito expresivo.</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>Analizar</t>
-        </is>
-      </c>
-      <c r="G72" s="3" t="inlineStr">
-        <is>
-          <t>• Describen percepciones, sentimientos e ideas que les genera la observación de manifestaciones visuales con temas de persona y medioambiente.
-• Describen características de materialidades, medios expresivos y lenguaje visual de manifestaciones visuales.
-• Interpretan significados de manifestaciones visuales con temas de persona y medioambiente.
-• Analizan relaciones entre manifestaciones visuales y sus contextos.
-• Describen funciones de manifestaciones visuales.
-• Comparan manifestaciones visuales usando criterios estéticos.
-• Determinan criterios estéticos para interpretar manifestaciones visuales.
-• Sintetizan información de sus investigaciones acerca de creadores y creadoras y manifestaciones visuales con temas de persona y naturaleza.
-• Comunican investigaciones y apreciaciones por medio de infografías y folletos.
-• Comunican investigaciones y apreciaciones por medio de infografías y presentaciones digitales.
-• Describen características de instalaciones considerando a la o al artista referente, uso de medios expresivos, materialidad y uso del lenguaje visual.
-• Describen características de la instalación considerando distribución espacial, recorridos e interacción con los espectadores.
-• Analizan relaciones entre temas y/o conceptos de las instalaciones, uso de medios expresivos, materialidad, lenguaje visual y propósito expresivo.
-• Analizan relaciones entre las instalaciones y sus contextos.
-• Interpretan significados de instalaciones considerando contexto, medios expresivos, materialidad, lenguaje visual y propósito expresivo.
-• Sintetizan información de sus investigaciones en torno a las instalaciones en una presentación.
-• Describen percepciones, sentimientos e ideas que les genera la observación de manifestaciones estéticas de diferentes épocas y contextos.
-• Infieren significados y propósitos de distintos diseños considerando aspectos del contexto, materialidad, lenguaje visual y propósito expresivo.
-• Relacionan el uso de lenguaje visual y elementos del diseño con sensaciones, emociones e ideas que este provoca.
-• Reconocen elementos culturales presentes en diseños de diferentes contextos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="4" t="inlineStr">
-        <is>
-          <t>8° Básico</t>
-        </is>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C73" s="5" t="inlineStr">
-        <is>
-          <t>Apreciar y responder frente al arte</t>
-        </is>
-      </c>
-      <c r="D73" s="4" t="inlineStr">
-        <is>
-          <t>OA 5</t>
-        </is>
-      </c>
-      <c r="E73" s="5" t="inlineStr">
-        <is>
-          <t>Evaluar trabajos visuales personales y de sus pares, considerando criterios como: materialidad, lenguaje visual y propósito expresivo.</t>
-        </is>
-      </c>
-      <c r="F73" s="4" t="inlineStr">
-        <is>
-          <t>Evaluar</t>
-        </is>
-      </c>
-      <c r="G73" s="5" t="inlineStr">
-        <is>
-          <t>• Explican ideas para sus trabajos visuales.
-• Explican fortalezas y elementos a mejorar en trabajos personales usando criterios de propósito expresivo, materialidad y utilización del lenguaje visual.
-• Explican fortalezas y elementos a mejorar en trabajos de sus pares usando criterios de propósito expresivo, materialidad y utilización del lenguaje visual.
-• Explican propósitos expresivos de trabajos personales.
-• Justifican la selección de materiales, herramientas y procedimientos desde el punto de vista de sus propósitos expresivos.
-• Justifican el uso del lenguaje visual en sus trabajos visuales según sus propósitos expresivos.
-• Coevalúan trabajos visuales usando criterios de propósito expresivo, materialidad y uso del lenguaje visual.
-• Coevalúan ideas para trabajos visuales usando criterios de propósito expresivo, materialidad y uso del lenguaje visual.
-• Identifican elementos originales de experimentaciones con diferentes materiales, herramientas y procedimientos.
-• Coevalúan las instalaciones usando criterios de propósito expresivo, medios expresivos, materialidad y uso del lenguaje visual.
-• Interpretan trabajos visuales e investigaciones de sus pares desde el punto de vista de la materialidad y propósito expresivo-funcional.</t>
-        </is>
-      </c>
-    </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
@@ -3979,7 +3981,7 @@
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -4020,7 +4022,7 @@
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -4077,7 +4079,7 @@
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C76" s="3" t="inlineStr">
@@ -4147,7 +4149,7 @@
       </c>
       <c r="B77" s="4" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -4219,7 +4221,7 @@
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C78" s="3" t="inlineStr">
@@ -4298,7 +4300,7 @@
       </c>
       <c r="B79" s="4" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -4372,7 +4374,7 @@
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>Artes visuales</t>
+          <t>Artes Visuales</t>
         </is>
       </c>
       <c r="C80" s="3" t="inlineStr">
@@ -4413,7 +4415,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="4" t="inlineStr"/>
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
       <c r="B81" s="4" t="inlineStr">
         <is>
           <t>Artes Visuales</t>
@@ -4421,25 +4427,638 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
+          <t>Artes Visuales, Audiovisuales y Multimediales</t>
+        </is>
+      </c>
+      <c r="D81" s="4" t="inlineStr">
+        <is>
+          <t>OA 1</t>
+        </is>
+      </c>
+      <c r="E81" s="5" t="inlineStr">
+        <is>
+          <t>Innovar al resolver desafíos y problemas de las artes visuales, audiovisuales y multimediales, considerando aspectos expresivos, estéticos y las evaluaciones críticas personal y de otros.</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>• Son innovadores al plantear propósitos expresivos y desarrollar ideas para cartografías.
+• Experimentan con variados soportes, materiales y procedimientos de artes visuales, para crear proyectos innovadores con el tema de la memoria personal y colectiva.
+• Experimentan con variados soportes, materiales y procedimientos de artes visuales, para crear proyectos innovadores.
+• Modifican proyectos de artes visuales basados en las evaluaciones críticas personales y de otros.
+• Experimentan con variados soportes, materiales y procedimientos de artes visuales, para crear esculturas innovadoras con el tema de la memoria colectiva del curso.
+• Innovan al experimentar con la integración de medios expresivos para crear una obra multimedial.
+• Resuelven de manera innovadora problemas que se presentan al desarrollar sus obras multimediales, considerando las evaluaciones personales y de otros.
+• Resuelven de manera innovadora aspectos expresivos y estéticos de la obra multimedial basada en la naturaleza.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C82" s="3" t="inlineStr">
+        <is>
+          <t>Expresar y crear</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>OA 1</t>
+        </is>
+      </c>
+      <c r="E82" s="3" t="inlineStr">
+        <is>
+          <t>Experimentar con diversidad de soportes, procedimientos y materiales utilizados en la ilustración, las artes audiovisuales y multimediales.</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>Aplicar</t>
+        </is>
+      </c>
+      <c r="G82" s="3" t="inlineStr">
+        <is>
+          <t>• En las experimentaciones con soportes, materiales y procedimientos, se observa maneras novedosas de trabajar con ellos.
+• En las experimentaciones con elementos de lenguaje visual, se observa maneras novedosas de trabajar con ellos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C83" s="5" t="inlineStr">
+        <is>
+          <t>Artes Visuales, Audiovisuales y Multimediales</t>
+        </is>
+      </c>
+      <c r="D83" s="4" t="inlineStr">
+        <is>
+          <t>OA 2</t>
+        </is>
+      </c>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>Crear obras y proyectos que respondan a necesidades de expresión y comunicación personales o grupales, basados en la investigación con soportes, materiales y procedimientos, y en referentes artísticos nacionales e internacionales.</t>
+        </is>
+      </c>
+      <c r="F83" s="4" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>• Desarrollan ideas creativas para cartografías con el tema de memoria personal y colectiva.
+• Experimentan con variados soportes, materiales y procedimientos de artes visuales, para crear proyectos innovadores con el tema de la memoria personal y colectiva.
+• Crean proyectos de artes visuales basados en sus imaginarios personales o grupales a partir del tema de la memoria personal y colectiva.
+• Experimentan con variados soportes, materiales y procedimientos de artes visuales, para crear proyectos innovadores.
+• Desarrollan ideas creativas para proyectos de artes visuales con el tema de la memoria y colectiva considerando propósito expresivo, descripción de la obra por medio de bocetos, elementos simbólicos, integración al contexto, plano del emplazamiento y cronología.
+• Experimentan con variados soportes, materiales y procedimientos de artes visuales, para crear esculturas innovadoras con el tema de la memoria colectiva del curso.
+• Crean obras y proyectos audiovisuales, relacionando propósitos expresivos, elementos de lenguaje audiovisual, simbólicos y contextos.
+• Desarrollan ideas creativas para retratos audiovisuales basados en sus imaginarios personales, sus intereses, referentes artísticos y temas presentes en su contexto.
+• Desarrollan ideas creativas para documentales poéticos basados en sus textos, imaginarios personales, sus intereses, referentes artísticos y temas presentes en su contexto.
+• Desarrollan ideas creativas para obras audiovisuales basados en sus imaginarios personales, sus intereses, referentes artísticos y temas presentes en su contexto.
+• Desarrollan ideas creativas para obras multimediales basados en sus imaginarios personales, sus intereses, referentes artísticos y temas presentes en su contexto.
+• Crean obras y proyectos multimediales, relacionando propósitos expresivos, uso de medios y lenguajes artísticos, elementos, simbólicos y contextos.
+• Desarrollan ideas creativas para obras multimediales de site specific basados en sus imaginarios personales, sus intereses, referentes artísticos y temas presentes en su contexto.
+• Crean obras y proyectos multimediales de site specific, relacionando propósitos expresivos, elementos simbólicos y contextos.
+• Desarrollan ideas creativas para obras multimediales basados en sus imaginarios personales, la naturaleza e intereses personales.
+• Desarrollan ideas creativas para obras multimediales sonoras basados en registros sonoros, sus imaginarios personales, sus intereses, referentes artísticos y temas presentes en su contexto.
+• Crean obras y proyectos multimediales sonoras, relacionando propósitos expresivos, elementos simbólicos y contextos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C84" s="3" t="inlineStr">
+        <is>
+          <t>Expresar y crear</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>OA 2</t>
+        </is>
+      </c>
+      <c r="E84" s="3" t="inlineStr">
+        <is>
+          <t>Crear obras y proyectos de ilustración, audiovisuales y multimediales, para expresar sensaciones, emociones e ideas, tomando riesgos creativos al seleccionar temas, materiales, soportes y procedimientos.</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t>• Los nanometrajes son originales en relación con el tratamiento del tema y el uso del lenguaje audiovisual.
+• En las experimentaciones se observa maneras novedosas de trabajar con materiales, procedimientos y lenguajes artísticos.
+• Los trabajos y proyectos artísticos audiovisuales, multimediales y de ilustración, son originales con respecto a los de sus compañeros.
+• Argumentan y justifican las decisiones y riesgos creativos tomados al elaborar sus trabajos y proyectos.
+• Desarrollan proyectos interdisciplinarios, considerando las ideas planteadas, actividades, roles, recursos y tiempos.
+• Resuelven problemas en el desarrollo de sus proyectos artísticos de manera autónoma y creativa.
+• Los resultados del proyecto expresan sensaciones, emociones o ideas de manera innovadora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C85" s="5" t="inlineStr">
+        <is>
+          <t>Artes Visuales, Audiovisuales y Multimediales</t>
+        </is>
+      </c>
+      <c r="D85" s="4" t="inlineStr">
+        <is>
+          <t>OA 3</t>
+        </is>
+      </c>
+      <c r="E85" s="5" t="inlineStr">
+        <is>
+          <t>Diseñar y gestionar presentaciones a públicos específicos para comunicar propósitos, aspectos del proceso y resultados de obras y trabajos, empleando materiales, herramientas y tecnologías tradicionales y emergentes.</t>
+        </is>
+      </c>
+      <c r="F85" s="4" t="inlineStr">
+        <is>
+          <t>Aplicar</t>
+        </is>
+      </c>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>• Diseñan proyectos de difusión de obras y proyectos de artes visuales, audiovisuales y multimediales.
+• Implementan sus proyectos de difusión, compartiéndolos con la comunidad.
+• Gestionan las tareas y roles asignados en sus planificaciones, aportando al trabajo colaborativo.
+• Crean diferentes piezas de diseño gráfico para difundir sus presentaciones en la comunidad.
+• Presentan a la comunidad su proceso y los resultados de sus creaciones artísticas por diferentes medios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C86" s="3" t="inlineStr">
+        <is>
+          <t>Expresar y crear</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>OA 3</t>
+        </is>
+      </c>
+      <c r="E86" s="3" t="inlineStr">
+        <is>
+          <t>Crear obras y proyectos de ilustración, audiovisuales o multimediales a partir de la apreciación de distintos referentes artísticos y culturales.</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G86" s="3" t="inlineStr">
+        <is>
+          <t>• Realizan proyectos artísticos, considerando las etapas del proceso creativo, recursos y tiempos.
+• Los resultados del proyecto son innovadores en relación con los de sus pares y expresan sensaciones, emociones o ideas.
+• En el proyecto hay una coherencia entre tema, lenguaje artístico, soportes, materiales y procedimientos, y propósito expresivo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>Artes Visuales, Audiovisuales y Multimediales</t>
+        </is>
+      </c>
+      <c r="D87" s="4" t="inlineStr">
+        <is>
+          <t>OA 4</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr">
+        <is>
+          <t>Analizar estéticamente obras visuales, audiovisuales y multimediales de diferentes épocas y procedencias, relacionando tratamiento de los lenguajes artísticos, elementos simbólicos y contextos.</t>
+        </is>
+      </c>
+      <c r="F87" s="4" t="inlineStr">
+        <is>
+          <t>Analizar</t>
+        </is>
+      </c>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>• Describen propósitos expresivos y significados de obras visuales cartográficas, considerando las sensaciones, emociones e ideas que generan.
+• Analizan relaciones entre medios expresivos, lenguajes artísticos, elementos simbólicos y contextos de obras visuales cartográficas.
+• Analizan relaciones entre propósito expresivo y uso de lenguaje visual de obras visuales.
+• Describen propósitos expresivos y significados de obras visuales con el tema de la memoria colectiva, considerando las sensaciones, emociones e ideas que generan.
+• Analizan relaciones entre propósito expresivo y uso de lenguaje visual.
+• Analizan relaciones entre elementos simbólicos y contextos.
+• Analizan obras audiovisuales nacionales e internacionales, considerando propósitos expresivos, uso de lenguaje audiovisual, elementos simbólicos y contextos.
+• Describen propósitos expresivos y significados de obras audiovisuales, considerando las sensaciones, emociones e ideas que les generan.
+• Analizan cómo el contexto y los propósitos expresivos determinan aspectos como medios, uso de elementos simbólicos y del lenguaje audiovisual.
+• Describen propósitos expresivos y significados de documentales poéticos, considerando las sensaciones, emociones e ideas que les generan.
+• Analizan relaciones entre propósito expresivo, lenguaje audiovisual, elementos simbólicos y contextos.
+• Interpretan propósitos expresivos y significados de obras multimediales, considerando las sensaciones, emociones e ideas que generan.
+• Analizan relaciones entre tratamiento de medios artísticos, contextos y sonidos.
+• Utilizan conceptos de las artes visuales, audiovisuales, multimediales y musicales para analizar e interpretar obras multimediales sonoras.
+• Analizan obras multimediales sonoras nacionales e internacionales, considerando propósitos expresivos, uso de los lenguajes artísticos, elementos simbólicos y contextos.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C88" s="3" t="inlineStr">
+        <is>
+          <t>Apreciar y responder</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>OA 4</t>
+        </is>
+      </c>
+      <c r="E88" s="3" t="inlineStr">
+        <is>
+          <t>Analizar e interpretar propósitos expresivos de obras visuales, audiovisuales y multimediales contemporáneas, a partir de criterios estéticos (lenguaje visual, materiales, procedimientos, emociones, sensaciones e ideas que genera, entre otros), utilizando conceptos disciplinarios.</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>Analizar</t>
+        </is>
+      </c>
+      <c r="G88" s="3" t="inlineStr">
+        <is>
+          <t>• Analizan características de soportes, procedimientos y materiales utilizados por ilustradores.
+• Relacionan propósitos expresivos de ilustraciones con emociones, sensaciones, lenguaje visual y materialidad.
+• Describen elementos y conceptos de lenguaje audiovisual presentes en videos y nanometrajes.
+• Establecen diferencias y semejanzas entre videos y nanometrajes, a partir del uso de elementos y conceptos de lenguaje audiovisual.
+• Interpretan propósitos expresivos y temas de obras multimediales a partir de las emociones, sensaciones e ideas que generan.
+• Relacionan propósitos expresivos con el uso de medios, soportes, procedimientos y materiales de obras multimediales.
+• Relacionan propósitos expresivos con elementos y conceptos de lenguaje visual y audiovisual de obras multimediales.
+• Interpretan elementos simbólicos presentes en obras multimediales.
+• Analizan relaciones entre los diferentes elementos o aspectos de obras multimediales y sus contextos.
+• Definen criterios estéticos para analizar obras visuales, audiovisuales y multimediales.
+• Analizan obras visuales, audiovisuales y multimediales a partir de criterios estéticos.
+• Argumentan juicios estéticos de ilustraciones, obras audiovisuales y multimediales, a partir de su análisis estético.
+• Argumentan juicios estéticos de ilustraciones, obras audiovisuales y multimediales, a partir del análisis de sus elementos simbólicos y aspectos contextuales.
+• Interpretan propósitos expresivos de ilustraciones, obras audiovisuales y multimediales con temas provenientes de otras disciplinas a partir de las emociones, sensaciones e ideas que generan.
+• Establecen relaciones coherentes entre propósito expresivo, tema, lenguaje artístico, soportes materiales y procedimientos.
+• Utilizan conceptos disciplinarios para analizar e interpretar propósitos expresivos de obras visuales, audiovisuales y multimediales contemporáneas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
+      <c r="B89" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>Artes Visuales, Audiovisuales y Multimediales</t>
+        </is>
+      </c>
+      <c r="D89" s="4" t="inlineStr">
+        <is>
+          <t>OA 5</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr">
+        <is>
+          <t>Argumentar juicios estéticos de obras visuales, audiovisuales y multimediales de diferentes épocas y procedencias, a partir de análisis estéticos e interpretaciones personales.</t>
+        </is>
+      </c>
+      <c r="F89" s="4" t="inlineStr">
+        <is>
+          <t>Evaluar</t>
+        </is>
+      </c>
+      <c r="G89" s="5" t="inlineStr">
+        <is>
+          <t>• Argumentan juicios estéticos de obras y proyectos audiovisuales a partir de interpretaciones personales, y del análisis de las relaciones entre propósito expresivo, contento y elementos simbólicos.
+• Argumentan juicios estéticos de obras y proyectos audiovisuales a partir de interpretaciones personales y de la relación de la obra con el contexto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C90" s="3" t="inlineStr">
+        <is>
+          <t>Apreciar y responder</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>OA 5</t>
+        </is>
+      </c>
+      <c r="E90" s="3" t="inlineStr">
+        <is>
+          <t>Argumentar juicios estéticos acerca de obras visuales, audiovisuales y multimediales contemporáneas, considerando propósitos expresivos, criterios estéticos, elementos simbólicos y aspectos contextuales.</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>Evaluar</t>
+        </is>
+      </c>
+      <c r="G90" s="3" t="inlineStr">
+        <is>
+          <t>• Argumentan juicios estéticos de ilustraciones, obras audiovisuales y multimediales, a partir de su análisis estético.
+• Argumentan juicios estéticos de ilustraciones, obras audiovisuales y multimediales, a partir del análisis de sus elementos simbólicos y aspectos contextuales.
+• Argumentan y justifican las ideas para sus proyectos, a partir de las relaciones establecidas con los referentes.
+• Evalúan ideas para sus proyectos artísticos, utilizando criterios estéticos pertinentes.
+• Evalúan críticamente ideas personales y de sus pares, basados en criterios de originalidad, selección de soportes, procedimientos, materiales y conceptos y elementos de los lenguajes artísticos y su coherencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
+      <c r="B91" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>Artes Visuales, Audiovisuales y Multimediales</t>
+        </is>
+      </c>
+      <c r="D91" s="4" t="inlineStr">
+        <is>
+          <t>OA 6</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr">
+        <is>
+          <t>Evaluar críticamente procesos y resultados de obras y proyectos personales y de sus pares, considerando relaciones entre propósitos expresivos y/o comunicativos, aspectos estéticos y decisiones tomadas durante el proceso.</t>
+        </is>
+      </c>
+      <c r="F91" s="4" t="inlineStr">
+        <is>
+          <t>Evaluar</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>• Evalúan críticamente obras visuales personales y de sus pares, basándose en criterios estéticos y propósitos expresivos.
+• Modifican proyectos de artes visuales basados en las evaluaciones críticas personales y de otros.
+• Evalúan críticamente obras visuales personales y de sus pares, basados en criterios estéticos y elementos como: propósito expresivo, bocetos, elementos simbólicos, integración al contexto, emplazamiento y cronología.
+• Evalúan críticamente obras visuales personales y de sus pares, basados en criterios estéticos.
+• Evalúan críticamente proyectos visuales personales y de sus pares, en relación con las decisiones tomadas durante el proceso.
+• Evalúan críticamente obras y proyectos audiovisuales personales y de sus pares, basados en criterios estéticos.
+• Evalúan críticamente las decisiones tomadas durante el proceso creativo y los resultados de estas.
+• Argumentan sus autoevaluaciones y las evaluaciones de sus pares, basados en criterios estéticos.
+• Evalúan críticamente experimentaciones personales y de sus pares, basados en criterios estéticos y de innovación.
+• Argumentan sus autoevaluaciones y las evaluaciones de sus pares, basados en criterios estéticos y de innovación.
+• Evalúan críticamente trabajos y proyectos de artes visuales, audiovisuales y multimediales para ser presentados a la comunidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr">
+        <is>
+          <t>Apreciar y responder</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>OA 6</t>
+        </is>
+      </c>
+      <c r="E92" s="3" t="inlineStr">
+        <is>
+          <t>Evaluar críticamente procesos y resultados de obras y proyectos visuales, audiovisuales y multimediales personales y de sus pares, considerando criterios estéticos y propósitos expresivos, y dando cuenta de una postura personal fundada y respetuosa.</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>Evaluar</t>
+        </is>
+      </c>
+      <c r="G92" s="3" t="inlineStr">
+        <is>
+          <t>• Evalúan críticamente experimentaciones e ideas personales y de sus pares, basados en criterios estéticos y desde una postura personal y respetuosa.
+• Evalúan ideas para sus proyectos artísticos, utilizando criterios estéticos pertinentes.
+• Evalúan críticamente ideas personales y de sus pares, basados en criterios de originalidad, selección de soportes, procedimientos, materiales y conceptos y elementos de los lenguajes artísticos y su coherencia.
+• Los criterios estéticos definidos son pertinentes para analizar y evaluar proyectos artísticos personales y de sus pares.
+• Argumentan sus autoevaluaciones y las evaluaciones de sus pares, a partir de criterios estéticos y desde una postura personal y respetuosa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>Artes Visuales, Audiovisuales y Multimediales</t>
+        </is>
+      </c>
+      <c r="D93" s="4" t="inlineStr">
+        <is>
+          <t>OA 7</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr">
+        <is>
+          <t>Relacionar, a partir de investigaciones, las habilidades y conocimientos de la asignatura con diferentes contextos laborales, profesionales y de desarrollo personal.</t>
+        </is>
+      </c>
+      <c r="F93" s="4" t="inlineStr">
+        <is>
+          <t>Analizar</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>• Identifican habilidades y conocimientos relacionados con las artes visuales, audiovisuales y multimediales.
+• Describen los roles y funciones de las artes visuales, audiovisuales y multimediales en la sociedad contemporánea.
+• Investigan acerca de posibilidades y contextos laborales y profesionales relacionadas con las artes visuales, audiovisuales y multimediales.
+• Reconocen por medio de la investigación posibilidades y contextos laborales y profesionales relacionadas con las artes visuales, audiovisuales y multimediales.
+• Difunden sus investigaciones a la comunidad escolar por diferentes medios.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>3 Y 4 Medio</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>Comunicar y difundir</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>OA 7</t>
+        </is>
+      </c>
+      <c r="E94" s="3" t="inlineStr">
+        <is>
+          <t>Diseñar y gestionar colaborativamente proyectos de difusión de obras visuales, audiovisuales y multimediales propios, empleando diversidad de medios o TIC.</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>Crear</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>• Analizan características de centros de difusión de las artes, basándose en criterios estéticos, funcionales y curatoriales.
+• Describen fortalezas y debilidades de centros de difusión de las artes.
+• Diseñan proyectos de difusión de artes visuales innovadores, considerando los diversos aspectos involucrados (espacios, público, gestión, recorridos, iluminación, montaje y difusión de la exposición).
+• Planifican sus proyectos de difusión, determinando actividades, roles y recursos.
+• Gestionan las tareas y roles asignados en sus planificaciones, aportando al trabajo colaborativo.
+• Realizan una muestra o exposición para difundir manifestaciones visuales de manera directa o a través de la web.
+• Resuelven problemas en el desarrollo de sus proyectos de difusión de manera autónoma y creativa.
+• Diseñan proyectos innovadores de difusión de manifestaciones visuales, audiovisuales y multimediales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>III y IV Medio</t>
+        </is>
+      </c>
+      <c r="B95" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C95" s="5" t="inlineStr">
+        <is>
           <t>Habilidades Artísticas Integradas</t>
         </is>
       </c>
-      <c r="D81" s="4" t="inlineStr">
+      <c r="D95" s="4" t="inlineStr">
         <is>
           <t>OA 1</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr">
+      <c r="E95" s="5" t="inlineStr">
         <is>
           <t>Innovar al resolver desafíos y problemas de las artes visuales, audiovisuales y multimediales, considerando aspectos expresivos, estéticos y las evaluaciones críticas personal y de otros.</t>
         </is>
       </c>
-      <c r="F81" s="4" t="inlineStr">
+      <c r="F95" s="4" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G81" s="5" t="inlineStr">
+      <c r="G95" s="5" t="inlineStr">
         <is>
           <t>• Son innovadores al plantear propósitos expresivos y desarrollar ideas para cartografías.
 • Desarrollan ideas creativas para cartografías con el tema de memoria personal y colectiva.
@@ -4452,34 +5071,38 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr"/>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C82" s="3" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>III y IV Medio</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C96" s="3" t="inlineStr">
         <is>
           <t>Habilidades Artísticas Integradas</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>OA 2</t>
         </is>
       </c>
-      <c r="E82" s="3" t="inlineStr">
+      <c r="E96" s="3" t="inlineStr">
         <is>
           <t>Crear obras y proyectos que respondan a necesidades de expresión y comunicación personales o grupales, basados en la investigación con soportes, materiales y procedimientos, y en referentes artísticos nacionales e internacionales.</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G82" s="3" t="inlineStr">
+      <c r="G96" s="3" t="inlineStr">
         <is>
           <t>• Son innovadores al plantear propósitos expresivos y desarrollar ideas para cartografías.
 • Desarrollan ideas creativas para cartografías con el tema de memoria personal y colectiva.
@@ -4502,34 +5125,38 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="4" t="inlineStr"/>
-      <c r="B83" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C83" s="5" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="4" t="inlineStr">
+        <is>
+          <t>III y IV Medio</t>
+        </is>
+      </c>
+      <c r="B97" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C97" s="5" t="inlineStr">
         <is>
           <t>Habilidades Artísticas Integradas</t>
         </is>
       </c>
-      <c r="D83" s="4" t="inlineStr">
+      <c r="D97" s="4" t="inlineStr">
         <is>
           <t>OA 3</t>
         </is>
       </c>
-      <c r="E83" s="5" t="inlineStr">
+      <c r="E97" s="5" t="inlineStr">
         <is>
           <t>Diseñar y gestionar presentaciones a públicos específicos para comunicar propósitos, aspectos del proceso y resultados de obras y trabajos, empleando materiales, herramientas y tecnologías tradicionales y emergentes.</t>
         </is>
       </c>
-      <c r="F83" s="4" t="inlineStr">
+      <c r="F97" s="4" t="inlineStr">
         <is>
           <t>Crear</t>
         </is>
       </c>
-      <c r="G83" s="5" t="inlineStr">
+      <c r="G97" s="5" t="inlineStr">
         <is>
           <t>• Diseñan proyectos de difusión de obras y proyectos de artes visuales, audiovisuales y multimediales.
 • Implementan sus proyectos de difusión, compartiéndolos con la comunidad.
@@ -4539,34 +5166,38 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr"/>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C84" s="3" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>III y IV Medio</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C98" s="3" t="inlineStr">
         <is>
           <t>Habilidades Artísticas Integradas</t>
         </is>
       </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>OA 4</t>
         </is>
       </c>
-      <c r="E84" s="3" t="inlineStr">
+      <c r="E98" s="3" t="inlineStr">
         <is>
           <t>Analizar estéticamente obras visuales, audiovisuales y multimediales de diferentes épocas y procedencias, relacionando tratamiento de los lenguajes artísticos, elementos simbólicos y contextos.</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Analizar</t>
         </is>
       </c>
-      <c r="G84" s="3" t="inlineStr">
+      <c r="G98" s="3" t="inlineStr">
         <is>
           <t>• Describen propósitos expresivos y significados de obras visuales cartográficas, considerando las sensaciones, emociones e ideas que generan.
 • Analizan relaciones entre medios expresivos, lenguajes artísticos, elementos simbólicos y contextos de obras visuales cartográficas.
@@ -4588,34 +5219,38 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="4" t="inlineStr"/>
-      <c r="B85" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C85" s="5" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="4" t="inlineStr">
+        <is>
+          <t>III y IV Medio</t>
+        </is>
+      </c>
+      <c r="B99" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C99" s="5" t="inlineStr">
         <is>
           <t>Habilidades Artísticas Integradas</t>
         </is>
       </c>
-      <c r="D85" s="4" t="inlineStr">
+      <c r="D99" s="4" t="inlineStr">
         <is>
           <t>OA 5</t>
         </is>
       </c>
-      <c r="E85" s="5" t="inlineStr">
+      <c r="E99" s="5" t="inlineStr">
         <is>
           <t>Argumentar juicios estéticos de obras visuales, audiovisuales y multimediales de diferentes épocas y procedencias, a partir de análisis estéticos e interpretaciones personales.</t>
         </is>
       </c>
-      <c r="F85" s="4" t="inlineStr">
+      <c r="F99" s="4" t="inlineStr">
         <is>
           <t>Evaluar</t>
         </is>
       </c>
-      <c r="G85" s="5" t="inlineStr">
+      <c r="G99" s="5" t="inlineStr">
         <is>
           <t>• Argumentan juicios estéticos de obras y proyectos audiovisuales a partir de interpretaciones personales, y del análisis de las relaciones entre propósito expresivo, contento y elementos simbólicos.
 • Argumentan juicios estéticos de obras y proyectos audiovisuales a partir de interpretaciones personales y de la relación de la obra con el contexto.
@@ -4623,34 +5258,38 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr"/>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C86" s="3" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>III y IV Medio</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C100" s="3" t="inlineStr">
         <is>
           <t>Habilidades Artísticas Integradas</t>
         </is>
       </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>OA 6</t>
         </is>
       </c>
-      <c r="E86" s="3" t="inlineStr">
+      <c r="E100" s="3" t="inlineStr">
         <is>
           <t>Evaluar críticamente procesos y resultados de obras y proyectos personales y de sus pares, considerando relaciones entre propósitos expresivos y/o comunicativos, aspectos estéticos y decisiones tomadas durante el proceso.</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Evaluar</t>
         </is>
       </c>
-      <c r="G86" s="3" t="inlineStr">
+      <c r="G100" s="3" t="inlineStr">
         <is>
           <t>• Evalúan críticamente obras visuales personales y de sus pares, basándose en criterios estéticos y propósitos expresivos.
 • Evalúan críticamente obras visuales personales y de sus pares, basados en criterios estéticos y elementos como: propósito expresivo, bocetos, elementos simbólicos, integración al contexto, emplazamiento y cronología.
@@ -4664,34 +5303,38 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="4" t="inlineStr"/>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t>Artes Visuales</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="4" t="inlineStr">
+        <is>
+          <t>III y IV Medio</t>
+        </is>
+      </c>
+      <c r="B101" s="4" t="inlineStr">
+        <is>
+          <t>Artes Visuales</t>
+        </is>
+      </c>
+      <c r="C101" s="5" t="inlineStr">
         <is>
           <t>Habilidades Artísticas Integradas</t>
         </is>
       </c>
-      <c r="D87" s="4" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>OA 7</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr">
+      <c r="E101" s="5" t="inlineStr">
         <is>
           <t>Relacionar, a partir de investigaciones, las habilidades y conocimientos de la asignatura con diferentes contextos laborales, profesionales y de desarrollo personal.</t>
         </is>
       </c>
-      <c r="F87" s="4" t="inlineStr">
+      <c r="F101" s="4" t="inlineStr">
         <is>
           <t>Analizar</t>
         </is>
       </c>
-      <c r="G87" s="5" t="inlineStr">
+      <c r="G101" s="5" t="inlineStr">
         <is>
           <t>• Identifican habilidades y conocimientos relacionados con las artes visuales, audiovisuales y multimediales.
 • Describen los roles y funciones de las artes visuales, audiovisuales y multimediales en la sociedad contemporánea.
@@ -4701,564 +5344,8 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr"/>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C88" s="3" t="inlineStr">
-        <is>
-          <t>Artes Visuales, Audiovisuales y Multimediales</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
-        <is>
-          <t>OA 1</t>
-        </is>
-      </c>
-      <c r="E88" s="3" t="inlineStr">
-        <is>
-          <t>Innovar al resolver desafíos y problemas de las artes visuales, audiovisuales y multimediales, considerando aspectos expresivos, estéticos y las evaluaciones críticas personal y de otros.</t>
-        </is>
-      </c>
-      <c r="F88" s="2" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G88" s="3" t="inlineStr">
-        <is>
-          <t>• Son innovadores al plantear propósitos expresivos y desarrollar ideas para cartografías.
-• Experimentan con variados soportes, materiales y procedimientos de artes visuales, para crear proyectos innovadores con el tema de la memoria personal y colectiva.
-• Experimentan con variados soportes, materiales y procedimientos de artes visuales, para crear proyectos innovadores.
-• Modifican proyectos de artes visuales basados en las evaluaciones críticas personales y de otros.
-• Experimentan con variados soportes, materiales y procedimientos de artes visuales, para crear esculturas innovadoras con el tema de la memoria colectiva del curso.
-• Innovan al experimentar con la integración de medios expresivos para crear una obra multimedial.
-• Resuelven de manera innovadora problemas que se presentan al desarrollar sus obras multimediales, considerando las evaluaciones personales y de otros.
-• Resuelven de manera innovadora aspectos expresivos y estéticos de la obra multimedial basada en la naturaleza.</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="4" t="inlineStr"/>
-      <c r="B89" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>Expresar y crear</t>
-        </is>
-      </c>
-      <c r="D89" s="4" t="inlineStr">
-        <is>
-          <t>OA 1</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr">
-        <is>
-          <t>Experimentar con diversidad de soportes, procedimientos y materiales utilizados en la ilustración, las artes audiovisuales y multimediales.</t>
-        </is>
-      </c>
-      <c r="F89" s="4" t="inlineStr">
-        <is>
-          <t>Aplicar</t>
-        </is>
-      </c>
-      <c r="G89" s="5" t="inlineStr">
-        <is>
-          <t>• En las experimentaciones con soportes, materiales y procedimientos, se observa maneras novedosas de trabajar con ellos.
-• En las experimentaciones con elementos de lenguaje visual, se observa maneras novedosas de trabajar con ellos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr"/>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C90" s="3" t="inlineStr">
-        <is>
-          <t>Artes Visuales, Audiovisuales y Multimediales</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
-        <is>
-          <t>OA 2</t>
-        </is>
-      </c>
-      <c r="E90" s="3" t="inlineStr">
-        <is>
-          <t>Crear obras y proyectos que respondan a necesidades de expresión y comunicación personales o grupales, basados en la investigación con soportes, materiales y procedimientos, y en referentes artísticos nacionales e internacionales.</t>
-        </is>
-      </c>
-      <c r="F90" s="2" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G90" s="3" t="inlineStr">
-        <is>
-          <t>• Desarrollan ideas creativas para cartografías con el tema de memoria personal y colectiva.
-• Experimentan con variados soportes, materiales y procedimientos de artes visuales, para crear proyectos innovadores con el tema de la memoria personal y colectiva.
-• Crean proyectos de artes visuales basados en sus imaginarios personales o grupales a partir del tema de la memoria personal y colectiva.
-• Experimentan con variados soportes, materiales y procedimientos de artes visuales, para crear proyectos innovadores.
-• Desarrollan ideas creativas para proyectos de artes visuales con el tema de la memoria y colectiva considerando propósito expresivo, descripción de la obra por medio de bocetos, elementos simbólicos, integración al contexto, plano del emplazamiento y cronología.
-• Experimentan con variados soportes, materiales y procedimientos de artes visuales, para crear esculturas innovadoras con el tema de la memoria colectiva del curso.
-• Crean obras y proyectos audiovisuales, relacionando propósitos expresivos, elementos de lenguaje audiovisual, simbólicos y contextos.
-• Desarrollan ideas creativas para retratos audiovisuales basados en sus imaginarios personales, sus intereses, referentes artísticos y temas presentes en su contexto.
-• Desarrollan ideas creativas para documentales poéticos basados en sus textos, imaginarios personales, sus intereses, referentes artísticos y temas presentes en su contexto.
-• Desarrollan ideas creativas para obras audiovisuales basados en sus imaginarios personales, sus intereses, referentes artísticos y temas presentes en su contexto.
-• Desarrollan ideas creativas para obras multimediales basados en sus imaginarios personales, sus intereses, referentes artísticos y temas presentes en su contexto.
-• Crean obras y proyectos multimediales, relacionando propósitos expresivos, uso de medios y lenguajes artísticos, elementos, simbólicos y contextos.
-• Desarrollan ideas creativas para obras multimediales de site specific basados en sus imaginarios personales, sus intereses, referentes artísticos y temas presentes en su contexto.
-• Crean obras y proyectos multimediales de site specific, relacionando propósitos expresivos, elementos simbólicos y contextos.
-• Desarrollan ideas creativas para obras multimediales basados en sus imaginarios personales, la naturaleza e intereses personales.
-• Desarrollan ideas creativas para obras multimediales sonoras basados en registros sonoros, sus imaginarios personales, sus intereses, referentes artísticos y temas presentes en su contexto.
-• Crean obras y proyectos multimediales sonoras, relacionando propósitos expresivos, elementos simbólicos y contextos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr"/>
-      <c r="B91" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>Expresar y crear</t>
-        </is>
-      </c>
-      <c r="D91" s="4" t="inlineStr">
-        <is>
-          <t>OA 2</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr">
-        <is>
-          <t>Crear obras y proyectos de ilustración, audiovisuales y multimediales, para expresar sensaciones, emociones e ideas, tomando riesgos creativos al seleccionar temas, materiales, soportes y procedimientos.</t>
-        </is>
-      </c>
-      <c r="F91" s="4" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G91" s="5" t="inlineStr">
-        <is>
-          <t>• Los nanometrajes son originales en relación con el tratamiento del tema y el uso del lenguaje audiovisual.
-• En las experimentaciones se observa maneras novedosas de trabajar con materiales, procedimientos y lenguajes artísticos.
-• Los trabajos y proyectos artísticos audiovisuales, multimediales y de ilustración, son originales con respecto a los de sus compañeros.
-• Argumentan y justifican las decisiones y riesgos creativos tomados al elaborar sus trabajos y proyectos.
-• Desarrollan proyectos interdisciplinarios, considerando las ideas planteadas, actividades, roles, recursos y tiempos.
-• Resuelven problemas en el desarrollo de sus proyectos artísticos de manera autónoma y creativa.
-• Los resultados del proyecto expresan sensaciones, emociones o ideas de manera innovadora.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr"/>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C92" s="3" t="inlineStr">
-        <is>
-          <t>Artes Visuales, Audiovisuales y Multimediales</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
-        <is>
-          <t>OA 3</t>
-        </is>
-      </c>
-      <c r="E92" s="3" t="inlineStr">
-        <is>
-          <t>Diseñar y gestionar presentaciones a públicos específicos para comunicar propósitos, aspectos del proceso y resultados de obras y trabajos, empleando materiales, herramientas y tecnologías tradicionales y emergentes.</t>
-        </is>
-      </c>
-      <c r="F92" s="2" t="inlineStr">
-        <is>
-          <t>Aplicar</t>
-        </is>
-      </c>
-      <c r="G92" s="3" t="inlineStr">
-        <is>
-          <t>• Diseñan proyectos de difusión de obras y proyectos de artes visuales, audiovisuales y multimediales.
-• Implementan sus proyectos de difusión, compartiéndolos con la comunidad.
-• Gestionan las tareas y roles asignados en sus planificaciones, aportando al trabajo colaborativo.
-• Crean diferentes piezas de diseño gráfico para difundir sus presentaciones en la comunidad.
-• Presentan a la comunidad su proceso y los resultados de sus creaciones artísticas por diferentes medios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="4" t="inlineStr"/>
-      <c r="B93" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>Expresar y crear</t>
-        </is>
-      </c>
-      <c r="D93" s="4" t="inlineStr">
-        <is>
-          <t>OA 3</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr">
-        <is>
-          <t>Crear obras y proyectos de ilustración, audiovisuales o multimediales a partir de la apreciación de distintos referentes artísticos y culturales.</t>
-        </is>
-      </c>
-      <c r="F93" s="4" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G93" s="5" t="inlineStr">
-        <is>
-          <t>• Realizan proyectos artísticos, considerando las etapas del proceso creativo, recursos y tiempos.
-• Los resultados del proyecto son innovadores en relación con los de sus pares y expresan sensaciones, emociones o ideas.
-• En el proyecto hay una coherencia entre tema, lenguaje artístico, soportes, materiales y procedimientos, y propósito expresivo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr"/>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C94" s="3" t="inlineStr">
-        <is>
-          <t>Artes Visuales, Audiovisuales y Multimediales</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>OA 4</t>
-        </is>
-      </c>
-      <c r="E94" s="3" t="inlineStr">
-        <is>
-          <t>Analizar estéticamente obras visuales, audiovisuales y multimediales de diferentes épocas y procedencias, relacionando tratamiento de los lenguajes artísticos, elementos simbólicos y contextos.</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Analizar</t>
-        </is>
-      </c>
-      <c r="G94" s="3" t="inlineStr">
-        <is>
-          <t>• Describen propósitos expresivos y significados de obras visuales cartográficas, considerando las sensaciones, emociones e ideas que generan.
-• Analizan relaciones entre medios expresivos, lenguajes artísticos, elementos simbólicos y contextos de obras visuales cartográficas.
-• Analizan relaciones entre propósito expresivo y uso de lenguaje visual de obras visuales.
-• Describen propósitos expresivos y significados de obras visuales con el tema de la memoria colectiva, considerando las sensaciones, emociones e ideas que generan.
-• Analizan relaciones entre propósito expresivo y uso de lenguaje visual.
-• Analizan relaciones entre elementos simbólicos y contextos.
-• Analizan obras audiovisuales nacionales e internacionales, considerando propósitos expresivos, uso de lenguaje audiovisual, elementos simbólicos y contextos.
-• Describen propósitos expresivos y significados de obras audiovisuales, considerando las sensaciones, emociones e ideas que les generan.
-• Analizan cómo el contexto y los propósitos expresivos determinan aspectos como medios, uso de elementos simbólicos y del lenguaje audiovisual.
-• Describen propósitos expresivos y significados de documentales poéticos, considerando las sensaciones, emociones e ideas que les generan.
-• Analizan relaciones entre propósito expresivo, lenguaje audiovisual, elementos simbólicos y contextos.
-• Interpretan propósitos expresivos y significados de obras multimediales, considerando las sensaciones, emociones e ideas que generan.
-• Analizan relaciones entre tratamiento de medios artísticos, contextos y sonidos.
-• Utilizan conceptos de las artes visuales, audiovisuales, multimediales y musicales para analizar e interpretar obras multimediales sonoras.
-• Analizan obras multimediales sonoras nacionales e internacionales, considerando propósitos expresivos, uso de los lenguajes artísticos, elementos simbólicos y contextos.</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" s="4" t="inlineStr"/>
-      <c r="B95" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C95" s="5" t="inlineStr">
-        <is>
-          <t>Apreciar y responder</t>
-        </is>
-      </c>
-      <c r="D95" s="4" t="inlineStr">
-        <is>
-          <t>OA 4</t>
-        </is>
-      </c>
-      <c r="E95" s="5" t="inlineStr">
-        <is>
-          <t>Analizar e interpretar propósitos expresivos de obras visuales, audiovisuales y multimediales contemporáneas, a partir de criterios estéticos (lenguaje visual, materiales, procedimientos, emociones, sensaciones e ideas que genera, entre otros), utilizando conceptos disciplinarios.</t>
-        </is>
-      </c>
-      <c r="F95" s="4" t="inlineStr">
-        <is>
-          <t>Analizar</t>
-        </is>
-      </c>
-      <c r="G95" s="5" t="inlineStr">
-        <is>
-          <t>• Analizan características de soportes, procedimientos y materiales utilizados por ilustradores.
-• Relacionan propósitos expresivos de ilustraciones con emociones, sensaciones, lenguaje visual y materialidad.
-• Describen elementos y conceptos de lenguaje audiovisual presentes en videos y nanometrajes.
-• Establecen diferencias y semejanzas entre videos y nanometrajes, a partir del uso de elementos y conceptos de lenguaje audiovisual.
-• Interpretan propósitos expresivos y temas de obras multimediales a partir de las emociones, sensaciones e ideas que generan.
-• Relacionan propósitos expresivos con el uso de medios, soportes, procedimientos y materiales de obras multimediales.
-• Relacionan propósitos expresivos con elementos y conceptos de lenguaje visual y audiovisual de obras multimediales.
-• Interpretan elementos simbólicos presentes en obras multimediales.
-• Analizan relaciones entre los diferentes elementos o aspectos de obras multimediales y sus contextos.
-• Definen criterios estéticos para analizar obras visuales, audiovisuales y multimediales.
-• Analizan obras visuales, audiovisuales y multimediales a partir de criterios estéticos.
-• Argumentan juicios estéticos de ilustraciones, obras audiovisuales y multimediales, a partir de su análisis estético.
-• Argumentan juicios estéticos de ilustraciones, obras audiovisuales y multimediales, a partir del análisis de sus elementos simbólicos y aspectos contextuales.
-• Interpretan propósitos expresivos de ilustraciones, obras audiovisuales y multimediales con temas provenientes de otras disciplinas a partir de las emociones, sensaciones e ideas que generan.
-• Establecen relaciones coherentes entre propósito expresivo, tema, lenguaje artístico, soportes materiales y procedimientos.
-• Utilizan conceptos disciplinarios para analizar e interpretar propósitos expresivos de obras visuales, audiovisuales y multimediales contemporáneas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr"/>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C96" s="3" t="inlineStr">
-        <is>
-          <t>Artes Visuales, Audiovisuales y Multimediales</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
-        <is>
-          <t>OA 5</t>
-        </is>
-      </c>
-      <c r="E96" s="3" t="inlineStr">
-        <is>
-          <t>Argumentar juicios estéticos de obras visuales, audiovisuales y multimediales de diferentes épocas y procedencias, a partir de análisis estéticos e interpretaciones personales.</t>
-        </is>
-      </c>
-      <c r="F96" s="2" t="inlineStr">
-        <is>
-          <t>Evaluar</t>
-        </is>
-      </c>
-      <c r="G96" s="3" t="inlineStr">
-        <is>
-          <t>• Argumentan juicios estéticos de obras y proyectos audiovisuales a partir de interpretaciones personales, y del análisis de las relaciones entre propósito expresivo, contento y elementos simbólicos.
-• Argumentan juicios estéticos de obras y proyectos audiovisuales a partir de interpretaciones personales y de la relación de la obra con el contexto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" s="4" t="inlineStr"/>
-      <c r="B97" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C97" s="5" t="inlineStr">
-        <is>
-          <t>Apreciar y responder</t>
-        </is>
-      </c>
-      <c r="D97" s="4" t="inlineStr">
-        <is>
-          <t>OA 5</t>
-        </is>
-      </c>
-      <c r="E97" s="5" t="inlineStr">
-        <is>
-          <t>Argumentar juicios estéticos acerca de obras visuales, audiovisuales y multimediales contemporáneas, considerando propósitos expresivos, criterios estéticos, elementos simbólicos y aspectos contextuales.</t>
-        </is>
-      </c>
-      <c r="F97" s="4" t="inlineStr">
-        <is>
-          <t>Evaluar</t>
-        </is>
-      </c>
-      <c r="G97" s="5" t="inlineStr">
-        <is>
-          <t>• Argumentan juicios estéticos de ilustraciones, obras audiovisuales y multimediales, a partir de su análisis estético.
-• Argumentan juicios estéticos de ilustraciones, obras audiovisuales y multimediales, a partir del análisis de sus elementos simbólicos y aspectos contextuales.
-• Argumentan y justifican las ideas para sus proyectos, a partir de las relaciones establecidas con los referentes.
-• Evalúan ideas para sus proyectos artísticos, utilizando criterios estéticos pertinentes.
-• Evalúan críticamente ideas personales y de sus pares, basados en criterios de originalidad, selección de soportes, procedimientos, materiales y conceptos y elementos de los lenguajes artísticos y su coherencia.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr"/>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C98" s="3" t="inlineStr">
-        <is>
-          <t>Artes Visuales, Audiovisuales y Multimediales</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>OA 6</t>
-        </is>
-      </c>
-      <c r="E98" s="3" t="inlineStr">
-        <is>
-          <t>Evaluar críticamente procesos y resultados de obras y proyectos personales y de sus pares, considerando relaciones entre propósitos expresivos y/o comunicativos, aspectos estéticos y decisiones tomadas durante el proceso.</t>
-        </is>
-      </c>
-      <c r="F98" s="2" t="inlineStr">
-        <is>
-          <t>Evaluar</t>
-        </is>
-      </c>
-      <c r="G98" s="3" t="inlineStr">
-        <is>
-          <t>• Evalúan críticamente obras visuales personales y de sus pares, basándose en criterios estéticos y propósitos expresivos.
-• Modifican proyectos de artes visuales basados en las evaluaciones críticas personales y de otros.
-• Evalúan críticamente obras visuales personales y de sus pares, basados en criterios estéticos y elementos como: propósito expresivo, bocetos, elementos simbólicos, integración al contexto, emplazamiento y cronología.
-• Evalúan críticamente obras visuales personales y de sus pares, basados en criterios estéticos.
-• Evalúan críticamente proyectos visuales personales y de sus pares, en relación con las decisiones tomadas durante el proceso.
-• Evalúan críticamente obras y proyectos audiovisuales personales y de sus pares, basados en criterios estéticos.
-• Evalúan críticamente las decisiones tomadas durante el proceso creativo y los resultados de estas.
-• Argumentan sus autoevaluaciones y las evaluaciones de sus pares, basados en criterios estéticos.
-• Evalúan críticamente experimentaciones personales y de sus pares, basados en criterios estéticos y de innovación.
-• Argumentan sus autoevaluaciones y las evaluaciones de sus pares, basados en criterios estéticos y de innovación.
-• Evalúan críticamente trabajos y proyectos de artes visuales, audiovisuales y multimediales para ser presentados a la comunidad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="4" t="inlineStr"/>
-      <c r="B99" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C99" s="5" t="inlineStr">
-        <is>
-          <t>Apreciar y responder</t>
-        </is>
-      </c>
-      <c r="D99" s="4" t="inlineStr">
-        <is>
-          <t>OA 6</t>
-        </is>
-      </c>
-      <c r="E99" s="5" t="inlineStr">
-        <is>
-          <t>Evaluar críticamente procesos y resultados de obras y proyectos visuales, audiovisuales y multimediales personales y de sus pares, considerando criterios estéticos y propósitos expresivos, y dando cuenta de una postura personal fundada y respetuosa.</t>
-        </is>
-      </c>
-      <c r="F99" s="4" t="inlineStr">
-        <is>
-          <t>Evaluar</t>
-        </is>
-      </c>
-      <c r="G99" s="5" t="inlineStr">
-        <is>
-          <t>• Evalúan críticamente experimentaciones e ideas personales y de sus pares, basados en criterios estéticos y desde una postura personal y respetuosa.
-• Evalúan ideas para sus proyectos artísticos, utilizando criterios estéticos pertinentes.
-• Evalúan críticamente ideas personales y de sus pares, basados en criterios de originalidad, selección de soportes, procedimientos, materiales y conceptos y elementos de los lenguajes artísticos y su coherencia.
-• Los criterios estéticos definidos son pertinentes para analizar y evaluar proyectos artísticos personales y de sus pares.
-• Argumentan sus autoevaluaciones y las evaluaciones de sus pares, a partir de criterios estéticos y desde una postura personal y respetuosa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr"/>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C100" s="3" t="inlineStr">
-        <is>
-          <t>Artes Visuales, Audiovisuales y Multimediales</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>OA 7</t>
-        </is>
-      </c>
-      <c r="E100" s="3" t="inlineStr">
-        <is>
-          <t>Relacionar, a partir de investigaciones, las habilidades y conocimientos de la asignatura con diferentes contextos laborales, profesionales y de desarrollo personal.</t>
-        </is>
-      </c>
-      <c r="F100" s="2" t="inlineStr">
-        <is>
-          <t>Analizar</t>
-        </is>
-      </c>
-      <c r="G100" s="3" t="inlineStr">
-        <is>
-          <t>• Identifican habilidades y conocimientos relacionados con las artes visuales, audiovisuales y multimediales.
-• Describen los roles y funciones de las artes visuales, audiovisuales y multimediales en la sociedad contemporánea.
-• Investigan acerca de posibilidades y contextos laborales y profesionales relacionadas con las artes visuales, audiovisuales y multimediales.
-• Reconocen por medio de la investigación posibilidades y contextos laborales y profesionales relacionadas con las artes visuales, audiovisuales y multimediales.
-• Difunden sus investigaciones a la comunidad escolar por diferentes medios.</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="4" t="inlineStr"/>
-      <c r="B101" s="4" t="inlineStr">
-        <is>
-          <t>Artes visuales</t>
-        </is>
-      </c>
-      <c r="C101" s="5" t="inlineStr">
-        <is>
-          <t>Comunicar y difundir</t>
-        </is>
-      </c>
-      <c r="D101" s="4" t="inlineStr">
-        <is>
-          <t>OA 7</t>
-        </is>
-      </c>
-      <c r="E101" s="5" t="inlineStr">
-        <is>
-          <t>Diseñar y gestionar colaborativamente proyectos de difusión de obras visuales, audiovisuales y multimediales propios, empleando diversidad de medios o TIC.</t>
-        </is>
-      </c>
-      <c r="F101" s="4" t="inlineStr">
-        <is>
-          <t>Crear</t>
-        </is>
-      </c>
-      <c r="G101" s="5" t="inlineStr">
-        <is>
-          <t>• Analizan características de centros de difusión de las artes, basándose en criterios estéticos, funcionales y curatoriales.
-• Describen fortalezas y debilidades de centros de difusión de las artes.
-• Diseñan proyectos de difusión de artes visuales innovadores, considerando los diversos aspectos involucrados (espacios, público, gestión, recorridos, iluminación, montaje y difusión de la exposición).
-• Planifican sus proyectos de difusión, determinando actividades, roles y recursos.
-• Gestionan las tareas y roles asignados en sus planificaciones, aportando al trabajo colaborativo.
-• Realizan una muestra o exposición para difundir manifestaciones visuales de manera directa o a través de la web.
-• Resuelven problemas en el desarrollo de sus proyectos de difusión de manera autónoma y creativa.
-• Diseñan proyectos innovadores de difusión de manifestaciones visuales, audiovisuales y multimediales.</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
+  <autoFilter ref="A1:G101"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>